--- a/compare/output/dscale_IndustryCO2_downscaled_SSP434.xlsx
+++ b/compare/output/dscale_IndustryCO2_downscaled_SSP434.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7206.835668</v>
+        <v>7202.463484</v>
       </c>
       <c r="F2" t="n">
-        <v>9865.677540999999</v>
+        <v>9862.585258999999</v>
       </c>
       <c r="G2" t="n">
-        <v>11665.943885</v>
+        <v>11663.763342</v>
       </c>
       <c r="H2" t="n">
-        <v>13294.917855</v>
+        <v>13293.468636</v>
       </c>
       <c r="I2" t="n">
-        <v>14476.079512</v>
+        <v>14475.342695</v>
       </c>
       <c r="J2" t="n">
         <v>15407.933193</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>242.4797</v>
+        <v>242.385682</v>
       </c>
       <c r="F3" t="n">
-        <v>379.647922</v>
+        <v>379.560489</v>
       </c>
       <c r="G3" t="n">
-        <v>505.239999</v>
+        <v>505.166303</v>
       </c>
       <c r="H3" t="n">
-        <v>636.664577</v>
+        <v>636.608222</v>
       </c>
       <c r="I3" t="n">
-        <v>741.136873</v>
+        <v>741.105409</v>
       </c>
       <c r="J3" t="n">
         <v>809.435229</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>111.000835</v>
+        <v>111.316633</v>
       </c>
       <c r="F4" t="n">
-        <v>174.489668</v>
+        <v>174.655356</v>
       </c>
       <c r="G4" t="n">
-        <v>241.817222</v>
+        <v>241.908369</v>
       </c>
       <c r="H4" t="n">
-        <v>304.950137</v>
+        <v>304.999758</v>
       </c>
       <c r="I4" t="n">
-        <v>343.914263</v>
+        <v>343.93573</v>
       </c>
       <c r="J4" t="n">
         <v>363.219413</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2529.434795</v>
+        <v>2528.042593</v>
       </c>
       <c r="F5" t="n">
-        <v>2886.298338</v>
+        <v>2885.531965</v>
       </c>
       <c r="G5" t="n">
-        <v>2688.276433</v>
+        <v>2687.923096</v>
       </c>
       <c r="H5" t="n">
-        <v>2598.804057</v>
+        <v>2598.652949</v>
       </c>
       <c r="I5" t="n">
-        <v>2557.573028</v>
+        <v>2557.521484</v>
       </c>
       <c r="J5" t="n">
         <v>2571.430385</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>27353.841612</v>
+        <v>27350.945724</v>
       </c>
       <c r="F6" t="n">
-        <v>36807.277636</v>
+        <v>36805.504683</v>
       </c>
       <c r="G6" t="n">
-        <v>48471.478459</v>
+        <v>48469.197883</v>
       </c>
       <c r="H6" t="n">
-        <v>61327.270758</v>
+        <v>61324.999035</v>
       </c>
       <c r="I6" t="n">
-        <v>70740.898791</v>
+        <v>70739.48148</v>
       </c>
       <c r="J6" t="n">
         <v>77206.54764600001</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8421.659193</v>
+        <v>8430.400401999999</v>
       </c>
       <c r="F7" t="n">
-        <v>11047.882264</v>
+        <v>11054.612577</v>
       </c>
       <c r="G7" t="n">
-        <v>12331.87785</v>
+        <v>12337.87475</v>
       </c>
       <c r="H7" t="n">
-        <v>13352.394866</v>
+        <v>13357.228545</v>
       </c>
       <c r="I7" t="n">
-        <v>13724.160334</v>
+        <v>13726.952125</v>
       </c>
       <c r="J7" t="n">
         <v>13776.221374</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7828.625251</v>
+        <v>7825.379446</v>
       </c>
       <c r="F8" t="n">
-        <v>10814.970098</v>
+        <v>10812.674655</v>
       </c>
       <c r="G8" t="n">
-        <v>12978.357278</v>
+        <v>12976.803132</v>
       </c>
       <c r="H8" t="n">
-        <v>15020.644004</v>
+        <v>15019.653021</v>
       </c>
       <c r="I8" t="n">
-        <v>16395.947715</v>
+        <v>16395.465075</v>
       </c>
       <c r="J8" t="n">
         <v>17375.137626</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>26.392739</v>
+        <v>27.18258</v>
       </c>
       <c r="F9" t="n">
-        <v>37.386101</v>
+        <v>37.823368</v>
       </c>
       <c r="G9" t="n">
-        <v>48.569744</v>
+        <v>48.824179</v>
       </c>
       <c r="H9" t="n">
-        <v>58.785393</v>
+        <v>58.928511</v>
       </c>
       <c r="I9" t="n">
-        <v>64.472505</v>
+        <v>64.53462399999999</v>
       </c>
       <c r="J9" t="n">
         <v>65.63238699999999</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2701.323248</v>
+        <v>2700.065485</v>
       </c>
       <c r="F10" t="n">
-        <v>4247.990966</v>
+        <v>4246.888969</v>
       </c>
       <c r="G10" t="n">
-        <v>6029.528559</v>
+        <v>6028.537847</v>
       </c>
       <c r="H10" t="n">
-        <v>7869.363625</v>
+        <v>7868.584807</v>
       </c>
       <c r="I10" t="n">
-        <v>9374.426025000001</v>
+        <v>9373.984681</v>
       </c>
       <c r="J10" t="n">
         <v>10540.059404</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4550.279515</v>
+        <v>4557.61379</v>
       </c>
       <c r="F11" t="n">
-        <v>6351.034791</v>
+        <v>6355.972469</v>
       </c>
       <c r="G11" t="n">
-        <v>7822.743703</v>
+        <v>7826.40429</v>
       </c>
       <c r="H11" t="n">
-        <v>9143.094816999999</v>
+        <v>9145.683908999999</v>
       </c>
       <c r="I11" t="n">
-        <v>10039.128984</v>
+        <v>10040.468315</v>
       </c>
       <c r="J11" t="n">
         <v>10756.122429</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5971.611331</v>
+        <v>5968.094811</v>
       </c>
       <c r="F12" t="n">
-        <v>7764.463166</v>
+        <v>7762.114191</v>
       </c>
       <c r="G12" t="n">
-        <v>8861.304174999999</v>
+        <v>8859.721323</v>
       </c>
       <c r="H12" t="n">
-        <v>9835.120244</v>
+        <v>9834.107791</v>
       </c>
       <c r="I12" t="n">
-        <v>10448.489451</v>
+        <v>10447.992342</v>
       </c>
       <c r="J12" t="n">
         <v>10730.4755</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7619.088713</v>
+        <v>7618.681968</v>
       </c>
       <c r="F13" t="n">
-        <v>11808.16121</v>
+        <v>11807.35572</v>
       </c>
       <c r="G13" t="n">
-        <v>16480.272205</v>
+        <v>16479.284999</v>
       </c>
       <c r="H13" t="n">
-        <v>21655.375014</v>
+        <v>21654.470163</v>
       </c>
       <c r="I13" t="n">
-        <v>26058.733207</v>
+        <v>26058.176728</v>
       </c>
       <c r="J13" t="n">
         <v>29729.675501</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>35361.93011</v>
+        <v>36903.226598</v>
       </c>
       <c r="F14" t="n">
-        <v>36805.035504</v>
+        <v>38119.51755</v>
       </c>
       <c r="G14" t="n">
-        <v>38317.184574</v>
+        <v>39323.07656</v>
       </c>
       <c r="H14" t="n">
-        <v>41054.470456</v>
+        <v>41784.841801</v>
       </c>
       <c r="I14" t="n">
-        <v>42799.005441</v>
+        <v>43203.454978</v>
       </c>
       <c r="J14" t="n">
         <v>43581.178239</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>62401.253983</v>
+        <v>61813.908089</v>
       </c>
       <c r="F15" t="n">
-        <v>74173.952051</v>
+        <v>73927.596365</v>
       </c>
       <c r="G15" t="n">
-        <v>81963.293899</v>
+        <v>81934.743953</v>
       </c>
       <c r="H15" t="n">
-        <v>91376.92200399999</v>
+        <v>91413.904129</v>
       </c>
       <c r="I15" t="n">
-        <v>98687.60112799999</v>
+        <v>98713.976588</v>
       </c>
       <c r="J15" t="n">
         <v>104056.076819</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6879.450615</v>
+        <v>7506.186033</v>
       </c>
       <c r="F16" t="n">
-        <v>6093.254395</v>
+        <v>6542.262321</v>
       </c>
       <c r="G16" t="n">
-        <v>5934.499383</v>
+        <v>6177.150277</v>
       </c>
       <c r="H16" t="n">
-        <v>6347.829344</v>
+        <v>6469.14788</v>
       </c>
       <c r="I16" t="n">
-        <v>6794.626292</v>
+        <v>6842.01893</v>
       </c>
       <c r="J16" t="n">
         <v>7180.452756</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20089.3742</v>
+        <v>18454.369022</v>
       </c>
       <c r="F17" t="n">
-        <v>26612.89193</v>
+        <v>24995.497366</v>
       </c>
       <c r="G17" t="n">
-        <v>31041.050926</v>
+        <v>29743.027639</v>
       </c>
       <c r="H17" t="n">
-        <v>35640.024263</v>
+        <v>34698.729575</v>
       </c>
       <c r="I17" t="n">
-        <v>39096.137271</v>
+        <v>38587.465763</v>
       </c>
       <c r="J17" t="n">
         <v>41691.981551</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7916.473846</v>
+        <v>7970.793012</v>
       </c>
       <c r="F18" t="n">
-        <v>8867.583793</v>
+        <v>8967.844071</v>
       </c>
       <c r="G18" t="n">
-        <v>9386.613396000001</v>
+        <v>9464.643749000001</v>
       </c>
       <c r="H18" t="n">
-        <v>10128.023104</v>
+        <v>10180.645786</v>
       </c>
       <c r="I18" t="n">
-        <v>10571.914244</v>
+        <v>10602.368117</v>
       </c>
       <c r="J18" t="n">
         <v>10688.484923</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1754.143948</v>
+        <v>1880.767994</v>
       </c>
       <c r="F19" t="n">
-        <v>2400.9679</v>
+        <v>2487.101799</v>
       </c>
       <c r="G19" t="n">
-        <v>3262.39008</v>
+        <v>3327.684424</v>
       </c>
       <c r="H19" t="n">
-        <v>4206.568629</v>
+        <v>4252.727907</v>
       </c>
       <c r="I19" t="n">
-        <v>5105.625945</v>
+        <v>5130.435895</v>
       </c>
       <c r="J19" t="n">
         <v>5912.742355</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>95.656627</v>
+        <v>103.297713</v>
       </c>
       <c r="F20" t="n">
-        <v>110.467352</v>
+        <v>115.540625</v>
       </c>
       <c r="G20" t="n">
-        <v>121.333135</v>
+        <v>125.264286</v>
       </c>
       <c r="H20" t="n">
-        <v>128.94108</v>
+        <v>131.699017</v>
       </c>
       <c r="I20" t="n">
-        <v>133.218971</v>
+        <v>134.650025</v>
       </c>
       <c r="J20" t="n">
         <v>134.638014</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>450.069174</v>
+        <v>447.905082</v>
       </c>
       <c r="F21" t="n">
-        <v>640.4889889999999</v>
+        <v>638.81457</v>
       </c>
       <c r="G21" t="n">
-        <v>844.4720160000001</v>
+        <v>843.07303</v>
       </c>
       <c r="H21" t="n">
-        <v>1017.265579</v>
+        <v>1016.237917</v>
       </c>
       <c r="I21" t="n">
-        <v>1130.938721</v>
+        <v>1130.389179</v>
       </c>
       <c r="J21" t="n">
         <v>1193.518779</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6528.32502</v>
+        <v>6507.764796</v>
       </c>
       <c r="F22" t="n">
-        <v>8633.739797</v>
+        <v>8621.157959</v>
       </c>
       <c r="G22" t="n">
-        <v>11071.803904</v>
+        <v>11062.094389</v>
       </c>
       <c r="H22" t="n">
-        <v>13623.37601</v>
+        <v>13615.997169</v>
       </c>
       <c r="I22" t="n">
-        <v>15884.630488</v>
+        <v>15880.361297</v>
       </c>
       <c r="J22" t="n">
         <v>17731.775</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5276.835723</v>
+        <v>5259.556354</v>
       </c>
       <c r="F23" t="n">
-        <v>7276.098616</v>
+        <v>7265.337203</v>
       </c>
       <c r="G23" t="n">
-        <v>9617.095853000001</v>
+        <v>9609.191693000001</v>
       </c>
       <c r="H23" t="n">
-        <v>12092.792789</v>
+        <v>12087.364985</v>
       </c>
       <c r="I23" t="n">
-        <v>14466.039785</v>
+        <v>14463.222626</v>
       </c>
       <c r="J23" t="n">
         <v>16700.953026</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>174.3466</v>
+        <v>179.523095</v>
       </c>
       <c r="F24" t="n">
-        <v>225.227655</v>
+        <v>228.545054</v>
       </c>
       <c r="G24" t="n">
-        <v>276.711223</v>
+        <v>279.181499</v>
       </c>
       <c r="H24" t="n">
-        <v>324.211484</v>
+        <v>325.923047</v>
       </c>
       <c r="I24" t="n">
-        <v>360.574716</v>
+        <v>361.474691</v>
       </c>
       <c r="J24" t="n">
         <v>386.14962</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>117.580272</v>
+        <v>119.101743</v>
       </c>
       <c r="F25" t="n">
-        <v>160.635591</v>
+        <v>161.426959</v>
       </c>
       <c r="G25" t="n">
-        <v>203.604798</v>
+        <v>204.093319</v>
       </c>
       <c r="H25" t="n">
-        <v>238.699638</v>
+        <v>239.003412</v>
       </c>
       <c r="I25" t="n">
-        <v>262.340475</v>
+        <v>262.492062</v>
       </c>
       <c r="J25" t="n">
         <v>277.7958</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>9742.124320000001</v>
+        <v>9707.955755000001</v>
       </c>
       <c r="F26" t="n">
-        <v>14327.091993</v>
+        <v>14299.87748</v>
       </c>
       <c r="G26" t="n">
-        <v>20495.552728</v>
+        <v>20469.34371</v>
       </c>
       <c r="H26" t="n">
-        <v>27522.246005</v>
+        <v>27499.611288</v>
       </c>
       <c r="I26" t="n">
-        <v>34619.412711</v>
+        <v>34605.112187</v>
       </c>
       <c r="J26" t="n">
         <v>41383.533201</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1954.364673</v>
+        <v>1966.232194</v>
       </c>
       <c r="F27" t="n">
-        <v>2863.159733</v>
+        <v>2870.428547</v>
       </c>
       <c r="G27" t="n">
-        <v>4087.052075</v>
+        <v>4091.223393</v>
       </c>
       <c r="H27" t="n">
-        <v>5494.697725</v>
+        <v>5496.744889</v>
       </c>
       <c r="I27" t="n">
-        <v>6915.155343</v>
+        <v>6915.863453</v>
       </c>
       <c r="J27" t="n">
         <v>8252.282227</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>14639.957479</v>
+        <v>14561.299111</v>
       </c>
       <c r="F28" t="n">
-        <v>18722.613445</v>
+        <v>18672.260874</v>
       </c>
       <c r="G28" t="n">
-        <v>20462.288567</v>
+        <v>20431.154635</v>
       </c>
       <c r="H28" t="n">
-        <v>20428.92391</v>
+        <v>20412.413217</v>
       </c>
       <c r="I28" t="n">
-        <v>19128.789269</v>
+        <v>19122.725008</v>
       </c>
       <c r="J28" t="n">
         <v>17576.484674</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3280.952411</v>
+        <v>3109.369053</v>
       </c>
       <c r="F29" t="n">
-        <v>5054.665538</v>
+        <v>4886.071568</v>
       </c>
       <c r="G29" t="n">
-        <v>7092.968601</v>
+        <v>6943.327145</v>
       </c>
       <c r="H29" t="n">
-        <v>9306.424519</v>
+        <v>9190.034181000001</v>
       </c>
       <c r="I29" t="n">
-        <v>11382.058359</v>
+        <v>11315.404115</v>
       </c>
       <c r="J29" t="n">
         <v>13336.314501</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6602.18718</v>
+        <v>6095.09542</v>
       </c>
       <c r="F30" t="n">
-        <v>11238.318412</v>
+        <v>10691.989444</v>
       </c>
       <c r="G30" t="n">
-        <v>17378.6654</v>
+        <v>16833.566636</v>
       </c>
       <c r="H30" t="n">
-        <v>24506.584263</v>
+        <v>24047.832533</v>
       </c>
       <c r="I30" t="n">
-        <v>31520.244197</v>
+        <v>31244.846765</v>
       </c>
       <c r="J30" t="n">
         <v>38266.932504</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1704.894886</v>
+        <v>1527.821299</v>
       </c>
       <c r="F31" t="n">
-        <v>2632.682672</v>
+        <v>2481.615685</v>
       </c>
       <c r="G31" t="n">
-        <v>3673.611188</v>
+        <v>3545.655395</v>
       </c>
       <c r="H31" t="n">
-        <v>4737.501837</v>
+        <v>4641.518339</v>
       </c>
       <c r="I31" t="n">
-        <v>5675.385773</v>
+        <v>5622.298714</v>
       </c>
       <c r="J31" t="n">
         <v>6517.090932</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6987.243599</v>
+        <v>6818.553735</v>
       </c>
       <c r="F32" t="n">
-        <v>10377.550765</v>
+        <v>10133.773673</v>
       </c>
       <c r="G32" t="n">
-        <v>14406.619765</v>
+        <v>14151.788411</v>
       </c>
       <c r="H32" t="n">
-        <v>18624.93935</v>
+        <v>18415.07366</v>
       </c>
       <c r="I32" t="n">
-        <v>22320.259653</v>
+        <v>22199.360789</v>
       </c>
       <c r="J32" t="n">
         <v>25589.245299</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6424.15946</v>
+        <v>6402.156294</v>
       </c>
       <c r="F33" t="n">
-        <v>9226.312347999999</v>
+        <v>9143.054128</v>
       </c>
       <c r="G33" t="n">
-        <v>12410.704779</v>
+        <v>12320.006532</v>
       </c>
       <c r="H33" t="n">
-        <v>15714.409746</v>
+        <v>15640.089458</v>
       </c>
       <c r="I33" t="n">
-        <v>18631.853331</v>
+        <v>18588.278982</v>
       </c>
       <c r="J33" t="n">
         <v>21280.947137</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>31655.159523</v>
+        <v>28369.773841</v>
       </c>
       <c r="F34" t="n">
-        <v>43335.776278</v>
+        <v>40931.056492</v>
       </c>
       <c r="G34" t="n">
-        <v>53309.922136</v>
+        <v>51610.655519</v>
       </c>
       <c r="H34" t="n">
-        <v>63816.108642</v>
+        <v>62705.071156</v>
       </c>
       <c r="I34" t="n">
-        <v>73621.97878999999</v>
+        <v>73062.153141</v>
       </c>
       <c r="J34" t="n">
         <v>83628.65169</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1775.416127</v>
+        <v>2137.425505</v>
       </c>
       <c r="F35" t="n">
-        <v>2151.258165</v>
+        <v>2499.685626</v>
       </c>
       <c r="G35" t="n">
-        <v>2612.332056</v>
+        <v>2962.424184</v>
       </c>
       <c r="H35" t="n">
-        <v>3051.113736</v>
+        <v>3344.258412</v>
       </c>
       <c r="I35" t="n">
-        <v>3394.922446</v>
+        <v>3563.426873</v>
       </c>
       <c r="J35" t="n">
         <v>3693.961235</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>128.82956</v>
+        <v>139.773362</v>
       </c>
       <c r="F36" t="n">
-        <v>156.785469</v>
+        <v>164.899884</v>
       </c>
       <c r="G36" t="n">
-        <v>189.886595</v>
+        <v>195.005649</v>
       </c>
       <c r="H36" t="n">
-        <v>222.17686</v>
+        <v>224.889136</v>
       </c>
       <c r="I36" t="n">
-        <v>246.989727</v>
+        <v>248.008175</v>
       </c>
       <c r="J36" t="n">
         <v>264.45022</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1436.38572</v>
+        <v>2184.871972</v>
       </c>
       <c r="F37" t="n">
-        <v>1076.477639</v>
+        <v>1563.987368</v>
       </c>
       <c r="G37" t="n">
-        <v>998.105647</v>
+        <v>1333.549062</v>
       </c>
       <c r="H37" t="n">
-        <v>993.447554</v>
+        <v>1211.759335</v>
       </c>
       <c r="I37" t="n">
-        <v>985.750612</v>
+        <v>1094.386679</v>
       </c>
       <c r="J37" t="n">
         <v>970.388174</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>8555.426267999999</v>
+        <v>8352.261044000001</v>
       </c>
       <c r="F38" t="n">
-        <v>12530.508159</v>
+        <v>12308.173986</v>
       </c>
       <c r="G38" t="n">
-        <v>17325.084897</v>
+        <v>17100.966343</v>
       </c>
       <c r="H38" t="n">
-        <v>22583.523239</v>
+        <v>22396.961406</v>
       </c>
       <c r="I38" t="n">
-        <v>27485.293034</v>
+        <v>27375.543791</v>
       </c>
       <c r="J38" t="n">
         <v>32058.116248</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3844.21682</v>
+        <v>3574.065524</v>
       </c>
       <c r="F39" t="n">
-        <v>5889.807502</v>
+        <v>5633.060762</v>
       </c>
       <c r="G39" t="n">
-        <v>8142.708288</v>
+        <v>7917.24258</v>
       </c>
       <c r="H39" t="n">
-        <v>10434.475381</v>
+        <v>10263.099926</v>
       </c>
       <c r="I39" t="n">
-        <v>12388.160459</v>
+        <v>12293.383491</v>
       </c>
       <c r="J39" t="n">
         <v>14066.720922</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>533.724503</v>
+        <v>487.38361</v>
       </c>
       <c r="F40" t="n">
-        <v>808.5578</v>
+        <v>768.533905</v>
       </c>
       <c r="G40" t="n">
-        <v>1106.804158</v>
+        <v>1073.124333</v>
       </c>
       <c r="H40" t="n">
-        <v>1419.232209</v>
+        <v>1393.865727</v>
       </c>
       <c r="I40" t="n">
-        <v>1694.500495</v>
+        <v>1680.425902</v>
       </c>
       <c r="J40" t="n">
         <v>1943.948822</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>517.798234</v>
+        <v>477.779882</v>
       </c>
       <c r="F41" t="n">
-        <v>780.583712</v>
+        <v>746.727814</v>
       </c>
       <c r="G41" t="n">
-        <v>1086.192867</v>
+        <v>1057.059786</v>
       </c>
       <c r="H41" t="n">
-        <v>1419.508809</v>
+        <v>1396.973996</v>
       </c>
       <c r="I41" t="n">
-        <v>1731.624156</v>
+        <v>1718.724344</v>
       </c>
       <c r="J41" t="n">
         <v>2027.823386</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1219.797847</v>
+        <v>1943.90142</v>
       </c>
       <c r="F42" t="n">
-        <v>869.893292</v>
+        <v>1395.463578</v>
       </c>
       <c r="G42" t="n">
-        <v>735.713808</v>
+        <v>1136.55075</v>
       </c>
       <c r="H42" t="n">
-        <v>641.051239</v>
+        <v>922.1160620000001</v>
       </c>
       <c r="I42" t="n">
-        <v>537.432743</v>
+        <v>684.949357</v>
       </c>
       <c r="J42" t="n">
         <v>421.77086</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2018.628229</v>
+        <v>1857.538212</v>
       </c>
       <c r="F43" t="n">
-        <v>3109.640698</v>
+        <v>2978.903949</v>
       </c>
       <c r="G43" t="n">
-        <v>4332.363123</v>
+        <v>4229.57931</v>
       </c>
       <c r="H43" t="n">
-        <v>5654.838877</v>
+        <v>5582.441676</v>
       </c>
       <c r="I43" t="n">
-        <v>6920.02006</v>
+        <v>6881.494332</v>
       </c>
       <c r="J43" t="n">
         <v>8164.566134</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5590.108622</v>
+        <v>5131.548531</v>
       </c>
       <c r="F44" t="n">
-        <v>8862.91827</v>
+        <v>8446.926864999999</v>
       </c>
       <c r="G44" t="n">
-        <v>12706.60749</v>
+        <v>12340.490862</v>
       </c>
       <c r="H44" t="n">
-        <v>16969.764382</v>
+        <v>16684.655365</v>
       </c>
       <c r="I44" t="n">
-        <v>21076.96963</v>
+        <v>20913.383473</v>
       </c>
       <c r="J44" t="n">
         <v>25037.827869</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1190.193343</v>
+        <v>1215.501012</v>
       </c>
       <c r="F45" t="n">
-        <v>1658.848711</v>
+        <v>1677.010981</v>
       </c>
       <c r="G45" t="n">
-        <v>2214.44652</v>
+        <v>2228.096579</v>
       </c>
       <c r="H45" t="n">
-        <v>2814.841489</v>
+        <v>2823.683077</v>
       </c>
       <c r="I45" t="n">
-        <v>3361.054095</v>
+        <v>3365.109553</v>
       </c>
       <c r="J45" t="n">
         <v>3860.559957</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7073.568074</v>
+        <v>6379.193747</v>
       </c>
       <c r="F46" t="n">
-        <v>11980.772682</v>
+        <v>11322.480095</v>
       </c>
       <c r="G46" t="n">
-        <v>18262.463802</v>
+        <v>17651.183322</v>
       </c>
       <c r="H46" t="n">
-        <v>25846.30362</v>
+        <v>25342.886475</v>
       </c>
       <c r="I46" t="n">
-        <v>33673.290113</v>
+        <v>33371.659391</v>
       </c>
       <c r="J46" t="n">
         <v>41943.359598</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>54585.223011</v>
+        <v>59327.124466</v>
       </c>
       <c r="F47" t="n">
-        <v>73063.90161</v>
+        <v>77501.352598</v>
       </c>
       <c r="G47" t="n">
-        <v>97084.815504</v>
+        <v>100901.58061</v>
       </c>
       <c r="H47" t="n">
-        <v>125226.491078</v>
+        <v>128141.474986</v>
       </c>
       <c r="I47" t="n">
-        <v>153244.849345</v>
+        <v>154903.481646</v>
       </c>
       <c r="J47" t="n">
         <v>181226.582584</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4722.920719</v>
+        <v>4895.124513</v>
       </c>
       <c r="F48" t="n">
-        <v>6767.974403</v>
+        <v>6851.719817</v>
       </c>
       <c r="G48" t="n">
-        <v>9346.423672999999</v>
+        <v>9386.569625</v>
       </c>
       <c r="H48" t="n">
-        <v>12275.025166</v>
+        <v>12287.329076</v>
       </c>
       <c r="I48" t="n">
-        <v>15152.256685</v>
+        <v>15149.161241</v>
       </c>
       <c r="J48" t="n">
         <v>18031.579876</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2061.794053</v>
+        <v>1890.85266</v>
       </c>
       <c r="F49" t="n">
-        <v>3117.06296</v>
+        <v>2971.38046</v>
       </c>
       <c r="G49" t="n">
-        <v>4317.360804</v>
+        <v>4193.428821</v>
       </c>
       <c r="H49" t="n">
-        <v>5625.427188</v>
+        <v>5530.375232</v>
       </c>
       <c r="I49" t="n">
-        <v>6861.197613</v>
+        <v>6806.971818</v>
       </c>
       <c r="J49" t="n">
         <v>8025.262519</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>49.014749</v>
+        <v>48.138347</v>
       </c>
       <c r="F50" t="n">
-        <v>67.364053</v>
+        <v>66.48805900000001</v>
       </c>
       <c r="G50" t="n">
-        <v>88.22428600000001</v>
+        <v>87.31447799999999</v>
       </c>
       <c r="H50" t="n">
-        <v>109.76794</v>
+        <v>108.963764</v>
       </c>
       <c r="I50" t="n">
-        <v>128.16788</v>
+        <v>127.665677</v>
       </c>
       <c r="J50" t="n">
         <v>143.601429</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3739.414917</v>
+        <v>3487.144981</v>
       </c>
       <c r="F51" t="n">
-        <v>5919.880705</v>
+        <v>5671.609025</v>
       </c>
       <c r="G51" t="n">
-        <v>8555.161688</v>
+        <v>8325.334510999999</v>
       </c>
       <c r="H51" t="n">
-        <v>11532.10739</v>
+        <v>11346.198069</v>
       </c>
       <c r="I51" t="n">
-        <v>14428.825258</v>
+        <v>14319.223919</v>
       </c>
       <c r="J51" t="n">
         <v>17228.166977</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2483.570648</v>
+        <v>2328.230073</v>
       </c>
       <c r="F52" t="n">
-        <v>3840.588507</v>
+        <v>3682.164589</v>
       </c>
       <c r="G52" t="n">
-        <v>5428.970226</v>
+        <v>5281.656859</v>
       </c>
       <c r="H52" t="n">
-        <v>7097.238035</v>
+        <v>6980.751502</v>
       </c>
       <c r="I52" t="n">
-        <v>8565.415838000001</v>
+        <v>8499.158127999999</v>
       </c>
       <c r="J52" t="n">
         <v>9840.354138000001</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>74509.66806700001</v>
+        <v>74592.486636</v>
       </c>
       <c r="F54" t="n">
-        <v>79651.905388</v>
+        <v>79702.34354</v>
       </c>
       <c r="G54" t="n">
-        <v>87084.283693</v>
+        <v>87120.66441899999</v>
       </c>
       <c r="H54" t="n">
-        <v>92670.21639099999</v>
+        <v>92693.952682</v>
       </c>
       <c r="I54" t="n">
-        <v>102908.340785</v>
+        <v>102920.556694</v>
       </c>
       <c r="J54" t="n">
         <v>110212.675676</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>18980.415431</v>
+        <v>18897.596862</v>
       </c>
       <c r="F55" t="n">
-        <v>20699.150989</v>
+        <v>20648.712837</v>
       </c>
       <c r="G55" t="n">
-        <v>22752.799357</v>
+        <v>22716.418631</v>
       </c>
       <c r="H55" t="n">
-        <v>24128.022638</v>
+        <v>24104.286348</v>
       </c>
       <c r="I55" t="n">
-        <v>26526.51905</v>
+        <v>26514.303142</v>
       </c>
       <c r="J55" t="n">
         <v>27963.627886</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>56.896992</v>
+        <v>56.955074</v>
       </c>
       <c r="F58" t="n">
-        <v>65.713187</v>
+        <v>65.74594999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>72.23826200000001</v>
+        <v>72.264712</v>
       </c>
       <c r="H58" t="n">
-        <v>76.117193</v>
+        <v>76.136123</v>
       </c>
       <c r="I58" t="n">
-        <v>78.538055</v>
+        <v>78.547864</v>
       </c>
       <c r="J58" t="n">
         <v>79.84892000000001</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>166.715714</v>
+        <v>166.255442</v>
       </c>
       <c r="F59" t="n">
-        <v>198.267152</v>
+        <v>198.040356</v>
       </c>
       <c r="G59" t="n">
-        <v>223.652954</v>
+        <v>223.528358</v>
       </c>
       <c r="H59" t="n">
-        <v>246.570169</v>
+        <v>246.500893</v>
       </c>
       <c r="I59" t="n">
-        <v>267.266404</v>
+        <v>267.234838</v>
       </c>
       <c r="J59" t="n">
         <v>285.973944</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>59.550251</v>
+        <v>59.744407</v>
       </c>
       <c r="F60" t="n">
-        <v>75.193583</v>
+        <v>75.252905</v>
       </c>
       <c r="G60" t="n">
-        <v>91.40438399999999</v>
+        <v>91.425499</v>
       </c>
       <c r="H60" t="n">
-        <v>102.107236</v>
+        <v>102.115433</v>
       </c>
       <c r="I60" t="n">
-        <v>106.79602</v>
+        <v>106.79907</v>
       </c>
       <c r="J60" t="n">
         <v>106.48124</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1813.97715</v>
+        <v>1815.144351</v>
       </c>
       <c r="F61" t="n">
-        <v>2135.426882</v>
+        <v>2136.066349</v>
       </c>
       <c r="G61" t="n">
-        <v>2501.762449</v>
+        <v>2502.155687</v>
       </c>
       <c r="H61" t="n">
-        <v>2821.232096</v>
+        <v>2821.445159</v>
       </c>
       <c r="I61" t="n">
-        <v>3093.085265</v>
+        <v>3093.16667</v>
       </c>
       <c r="J61" t="n">
         <v>3293.745795</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3573.799202</v>
+        <v>3595.260849</v>
       </c>
       <c r="F62" t="n">
-        <v>3415.18544</v>
+        <v>3428.16156</v>
       </c>
       <c r="G62" t="n">
-        <v>3365.44469</v>
+        <v>3373.879863</v>
       </c>
       <c r="H62" t="n">
-        <v>3310.308676</v>
+        <v>3315.270515</v>
       </c>
       <c r="I62" t="n">
-        <v>3245.859695</v>
+        <v>3248.058846</v>
       </c>
       <c r="J62" t="n">
         <v>3147.530348</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3992.767302</v>
+        <v>4000.880586</v>
       </c>
       <c r="F63" t="n">
-        <v>4404.475947</v>
+        <v>4409.422891</v>
       </c>
       <c r="G63" t="n">
-        <v>5005.843555</v>
+        <v>5008.893565</v>
       </c>
       <c r="H63" t="n">
-        <v>5498.720865</v>
+        <v>5500.473101</v>
       </c>
       <c r="I63" t="n">
-        <v>5833.736749</v>
+        <v>5834.526905</v>
       </c>
       <c r="J63" t="n">
         <v>5957.475003</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>38.400725</v>
+        <v>38.307207</v>
       </c>
       <c r="F64" t="n">
-        <v>44.035496</v>
+        <v>43.990258</v>
       </c>
       <c r="G64" t="n">
-        <v>48.18127</v>
+        <v>48.156963</v>
       </c>
       <c r="H64" t="n">
-        <v>50.324749</v>
+        <v>50.311931</v>
       </c>
       <c r="I64" t="n">
-        <v>51.056585</v>
+        <v>51.051137</v>
       </c>
       <c r="J64" t="n">
         <v>50.695189</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>10294.445147</v>
+        <v>10277.231493</v>
       </c>
       <c r="F65" t="n">
-        <v>12529.870166</v>
+        <v>12521.653712</v>
       </c>
       <c r="G65" t="n">
-        <v>15031.051009</v>
+        <v>15026.584644</v>
       </c>
       <c r="H65" t="n">
-        <v>17425.751279</v>
+        <v>17423.294882</v>
       </c>
       <c r="I65" t="n">
-        <v>19616.0998</v>
+        <v>19614.985201</v>
       </c>
       <c r="J65" t="n">
         <v>21606.05655</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8827.154307999999</v>
+        <v>8810.465555000001</v>
       </c>
       <c r="F66" t="n">
-        <v>10537.034471</v>
+        <v>10529.069123</v>
       </c>
       <c r="G66" t="n">
-        <v>12348.685891</v>
+        <v>12344.347247</v>
       </c>
       <c r="H66" t="n">
-        <v>13963.308048</v>
+        <v>13960.932934</v>
       </c>
       <c r="I66" t="n">
-        <v>15358.326826</v>
+        <v>15357.259011</v>
       </c>
       <c r="J66" t="n">
         <v>16569.013472</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>27249.346915</v>
+        <v>27169.074106</v>
       </c>
       <c r="F67" t="n">
-        <v>29580.84049</v>
+        <v>29544.821093</v>
       </c>
       <c r="G67" t="n">
-        <v>30960.305631</v>
+        <v>30941.886756</v>
       </c>
       <c r="H67" t="n">
-        <v>31518.601397</v>
+        <v>31509.180316</v>
       </c>
       <c r="I67" t="n">
-        <v>31492.102349</v>
+        <v>31488.185683</v>
       </c>
       <c r="J67" t="n">
         <v>31008.448854</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1254.119817</v>
+        <v>1260.13055</v>
       </c>
       <c r="F68" t="n">
-        <v>1214.777843</v>
+        <v>1218.656518</v>
       </c>
       <c r="G68" t="n">
-        <v>1116.722187</v>
+        <v>1119.723048</v>
       </c>
       <c r="H68" t="n">
-        <v>1024.462977</v>
+        <v>1026.496763</v>
       </c>
       <c r="I68" t="n">
-        <v>960.973173</v>
+        <v>961.969838</v>
       </c>
       <c r="J68" t="n">
         <v>917.234252</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>57.678976</v>
+        <v>57.539705</v>
       </c>
       <c r="F69" t="n">
-        <v>65.565724</v>
+        <v>65.500598</v>
       </c>
       <c r="G69" t="n">
-        <v>73.08137600000001</v>
+        <v>73.046137</v>
       </c>
       <c r="H69" t="n">
-        <v>78.714371</v>
+        <v>78.695239</v>
       </c>
       <c r="I69" t="n">
-        <v>82.443973</v>
+        <v>82.435551</v>
       </c>
       <c r="J69" t="n">
         <v>83.45222800000001</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>10540.46913</v>
+        <v>10512.002408</v>
       </c>
       <c r="F70" t="n">
-        <v>11731.512919</v>
+        <v>11718.488188</v>
       </c>
       <c r="G70" t="n">
-        <v>12655.078419</v>
+        <v>12648.267563</v>
       </c>
       <c r="H70" t="n">
-        <v>13153.161334</v>
+        <v>13149.619673</v>
       </c>
       <c r="I70" t="n">
-        <v>13325.581443</v>
+        <v>13324.089305</v>
       </c>
       <c r="J70" t="n">
         <v>13174.145097</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1323.50214</v>
+        <v>1331.489594</v>
       </c>
       <c r="F71" t="n">
-        <v>1387.44659</v>
+        <v>1392.431835</v>
       </c>
       <c r="G71" t="n">
-        <v>1545.731683</v>
+        <v>1548.918324</v>
       </c>
       <c r="H71" t="n">
-        <v>1716.993113</v>
+        <v>1718.838</v>
       </c>
       <c r="I71" t="n">
-        <v>1880.256661</v>
+        <v>1881.071644</v>
       </c>
       <c r="J71" t="n">
         <v>1998.954312</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4041.049557</v>
+        <v>4033.970021</v>
       </c>
       <c r="F72" t="n">
-        <v>4540.398606</v>
+        <v>4537.101828</v>
       </c>
       <c r="G72" t="n">
-        <v>4922.847831</v>
+        <v>4921.156094</v>
       </c>
       <c r="H72" t="n">
-        <v>5086.351215</v>
+        <v>5085.502177</v>
       </c>
       <c r="I72" t="n">
-        <v>5068.950525</v>
+        <v>5068.611583</v>
       </c>
       <c r="J72" t="n">
         <v>4904.295696</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>382.459841</v>
+        <v>488.008428</v>
       </c>
       <c r="F73" t="n">
-        <v>324.972119</v>
+        <v>366.359226</v>
       </c>
       <c r="G73" t="n">
-        <v>381.420336</v>
+        <v>399.239208</v>
       </c>
       <c r="H73" t="n">
-        <v>457.624202</v>
+        <v>465.546932</v>
       </c>
       <c r="I73" t="n">
-        <v>502.324201</v>
+        <v>505.409358</v>
       </c>
       <c r="J73" t="n">
         <v>504.834365</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>47.649016</v>
+        <v>47.522405</v>
       </c>
       <c r="F74" t="n">
-        <v>44.478728</v>
+        <v>44.432954</v>
       </c>
       <c r="G74" t="n">
-        <v>45.018744</v>
+        <v>44.997003</v>
       </c>
       <c r="H74" t="n">
-        <v>46.28799</v>
+        <v>46.27684</v>
       </c>
       <c r="I74" t="n">
-        <v>47.169672</v>
+        <v>47.164891</v>
       </c>
       <c r="J74" t="n">
         <v>46.906117</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4922.404624</v>
+        <v>4792.70955</v>
       </c>
       <c r="F75" t="n">
-        <v>5554.402755</v>
+        <v>5436.277854</v>
       </c>
       <c r="G75" t="n">
-        <v>6115.635203</v>
+        <v>6006.004868</v>
       </c>
       <c r="H75" t="n">
-        <v>6160.598169</v>
+        <v>6083.154495</v>
       </c>
       <c r="I75" t="n">
-        <v>5961.860683</v>
+        <v>5925.301914</v>
       </c>
       <c r="J75" t="n">
         <v>5533.258882</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10034.179451</v>
+        <v>10057.238318</v>
       </c>
       <c r="F76" t="n">
-        <v>11956.481711</v>
+        <v>11959.71314</v>
       </c>
       <c r="G76" t="n">
-        <v>15655.897924</v>
+        <v>15546.171311</v>
       </c>
       <c r="H76" t="n">
-        <v>18316.13674</v>
+        <v>18167.634804</v>
       </c>
       <c r="I76" t="n">
-        <v>19725.796732</v>
+        <v>19632.991401</v>
       </c>
       <c r="J76" t="n">
         <v>19568.514892</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6950.577879</v>
+        <v>6879.698513</v>
       </c>
       <c r="F77" t="n">
-        <v>7096.397243</v>
+        <v>7068.781035</v>
       </c>
       <c r="G77" t="n">
-        <v>7396.474693</v>
+        <v>7390.311105</v>
       </c>
       <c r="H77" t="n">
-        <v>7303.698981</v>
+        <v>7296.860995</v>
       </c>
       <c r="I77" t="n">
-        <v>7121.47838</v>
+        <v>7112.901212</v>
       </c>
       <c r="J77" t="n">
         <v>6728.023273</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>23717.699768</v>
+        <v>26145.45036</v>
       </c>
       <c r="F78" t="n">
-        <v>28226.721283</v>
+        <v>29918.265811</v>
       </c>
       <c r="G78" t="n">
-        <v>34757.919636</v>
+        <v>35921.086708</v>
       </c>
       <c r="H78" t="n">
-        <v>38120.030411</v>
+        <v>38735.876106</v>
       </c>
       <c r="I78" t="n">
-        <v>39204.364887</v>
+        <v>39440.282496</v>
       </c>
       <c r="J78" t="n">
         <v>38136.742342</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>14276.372052</v>
+        <v>13897.468146</v>
       </c>
       <c r="F79" t="n">
-        <v>14945.371764</v>
+        <v>14663.656761</v>
       </c>
       <c r="G79" t="n">
-        <v>15153.935741</v>
+        <v>14961.664922</v>
       </c>
       <c r="H79" t="n">
-        <v>14402.241336</v>
+        <v>14305.388192</v>
       </c>
       <c r="I79" t="n">
-        <v>13533.025043</v>
+        <v>13499.058028</v>
       </c>
       <c r="J79" t="n">
         <v>12501.332673</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7519.703836</v>
+        <v>7370.605865</v>
       </c>
       <c r="F80" t="n">
-        <v>10356.091223</v>
+        <v>10152.496118</v>
       </c>
       <c r="G80" t="n">
-        <v>13693.146122</v>
+        <v>13440.266042</v>
       </c>
       <c r="H80" t="n">
-        <v>15514.982189</v>
+        <v>15305.888283</v>
       </c>
       <c r="I80" t="n">
-        <v>16139.010323</v>
+        <v>16031.948406</v>
       </c>
       <c r="J80" t="n">
         <v>15744.493262</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>19645.263736</v>
+        <v>19006.058301</v>
       </c>
       <c r="F81" t="n">
-        <v>20763.539996</v>
+        <v>20237.112992</v>
       </c>
       <c r="G81" t="n">
-        <v>21612.03411</v>
+        <v>21166.798699</v>
       </c>
       <c r="H81" t="n">
-        <v>21173.002611</v>
+        <v>20880.080478</v>
       </c>
       <c r="I81" t="n">
-        <v>20398.400773</v>
+        <v>20265.882161</v>
       </c>
       <c r="J81" t="n">
         <v>19363.384184</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>8557.992774</v>
+        <v>8810.113665999999</v>
       </c>
       <c r="F82" t="n">
-        <v>10219.022363</v>
+        <v>10420.084021</v>
       </c>
       <c r="G82" t="n">
-        <v>12212.904985</v>
+        <v>12371.056299</v>
       </c>
       <c r="H82" t="n">
-        <v>12928.143747</v>
+        <v>13026.762749</v>
       </c>
       <c r="I82" t="n">
-        <v>12883.991172</v>
+        <v>12928.319213</v>
       </c>
       <c r="J82" t="n">
         <v>12220.769974</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>70276.81675300001</v>
+        <v>68941.66815500001</v>
       </c>
       <c r="F83" t="n">
-        <v>73201.079927</v>
+        <v>72462.72053200001</v>
       </c>
       <c r="G83" t="n">
-        <v>75656.675345</v>
+        <v>75451.263804</v>
       </c>
       <c r="H83" t="n">
-        <v>72885.14861800001</v>
+        <v>73002.3367</v>
       </c>
       <c r="I83" t="n">
-        <v>68914.985607</v>
+        <v>69046.22877</v>
       </c>
       <c r="J83" t="n">
         <v>63966.394306</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>14534.163396</v>
+        <v>14505.952342</v>
       </c>
       <c r="F86" t="n">
-        <v>14350.41276</v>
+        <v>14335.226176</v>
       </c>
       <c r="G86" t="n">
-        <v>15226.233894</v>
+        <v>15215.6641</v>
       </c>
       <c r="H86" t="n">
-        <v>15056.51733</v>
+        <v>15050.077309</v>
       </c>
       <c r="I86" t="n">
-        <v>14578.446216</v>
+        <v>14575.499429</v>
       </c>
       <c r="J86" t="n">
         <v>13662.147321</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1545.299195</v>
+        <v>1545.327513</v>
       </c>
       <c r="F87" t="n">
-        <v>1612.17259</v>
+        <v>1612.517763</v>
       </c>
       <c r="G87" t="n">
-        <v>1744.124429</v>
+        <v>1744.741257</v>
       </c>
       <c r="H87" t="n">
-        <v>1761.639571</v>
+        <v>1762.162556</v>
       </c>
       <c r="I87" t="n">
-        <v>1753.709391</v>
+        <v>1753.979301</v>
       </c>
       <c r="J87" t="n">
         <v>1698.886009</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13037.284241</v>
+        <v>13105.849559</v>
       </c>
       <c r="F88" t="n">
-        <v>15108.037969</v>
+        <v>15129.728092</v>
       </c>
       <c r="G88" t="n">
-        <v>18142.51295</v>
+        <v>18148.538813</v>
       </c>
       <c r="H88" t="n">
-        <v>19227.963781</v>
+        <v>19228.843083</v>
       </c>
       <c r="I88" t="n">
-        <v>19220.394865</v>
+        <v>19220.344284</v>
       </c>
       <c r="J88" t="n">
         <v>18222.042679</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2077.027797</v>
+        <v>2106.226148</v>
       </c>
       <c r="F89" t="n">
-        <v>2154.730796</v>
+        <v>2169.149511</v>
       </c>
       <c r="G89" t="n">
-        <v>2303.515338</v>
+        <v>2312.848825</v>
       </c>
       <c r="H89" t="n">
-        <v>2270.97809</v>
+        <v>2276.23093</v>
       </c>
       <c r="I89" t="n">
-        <v>2187.331843</v>
+        <v>2189.562358</v>
       </c>
       <c r="J89" t="n">
         <v>2042.573042</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>15102.877427</v>
+        <v>15086.23738</v>
       </c>
       <c r="F90" t="n">
-        <v>15623.953225</v>
+        <v>15611.648755</v>
       </c>
       <c r="G90" t="n">
-        <v>16442.517638</v>
+        <v>16434.950538</v>
       </c>
       <c r="H90" t="n">
-        <v>15834.131728</v>
+        <v>15830.571197</v>
       </c>
       <c r="I90" t="n">
-        <v>14876.113986</v>
+        <v>14874.90502</v>
       </c>
       <c r="J90" t="n">
         <v>13556.239225</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5256.153274</v>
+        <v>5258.322842</v>
       </c>
       <c r="F91" t="n">
-        <v>5231.49075</v>
+        <v>5232.453114</v>
       </c>
       <c r="G91" t="n">
-        <v>5502.713025</v>
+        <v>5503.28643</v>
       </c>
       <c r="H91" t="n">
-        <v>5417.088798</v>
+        <v>5417.194314</v>
       </c>
       <c r="I91" t="n">
-        <v>5237.917697</v>
+        <v>5237.818885</v>
       </c>
       <c r="J91" t="n">
         <v>4904.677626</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3876.132169</v>
+        <v>3860.157957</v>
       </c>
       <c r="F92" t="n">
-        <v>3800.0528</v>
+        <v>3791.641732</v>
       </c>
       <c r="G92" t="n">
-        <v>3869.760356</v>
+        <v>3864.60379</v>
       </c>
       <c r="H92" t="n">
-        <v>3721.424</v>
+        <v>3718.585728</v>
       </c>
       <c r="I92" t="n">
-        <v>3550.433899</v>
+        <v>3549.218159</v>
       </c>
       <c r="J92" t="n">
         <v>3305.763502</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>507.027939</v>
+        <v>504.286624</v>
       </c>
       <c r="F93" t="n">
-        <v>519.72765</v>
+        <v>518.212709</v>
       </c>
       <c r="G93" t="n">
-        <v>540.1922530000001</v>
+        <v>539.229261</v>
       </c>
       <c r="H93" t="n">
-        <v>512.323123</v>
+        <v>511.80678</v>
       </c>
       <c r="I93" t="n">
-        <v>475.265935</v>
+        <v>475.057561</v>
       </c>
       <c r="J93" t="n">
         <v>430.298638</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>54115.792861</v>
+        <v>54130.957595</v>
       </c>
       <c r="F94" t="n">
-        <v>52809.498716</v>
+        <v>52832.946577</v>
       </c>
       <c r="G94" t="n">
-        <v>55344.061448</v>
+        <v>55365.29851</v>
       </c>
       <c r="H94" t="n">
-        <v>54099.438214</v>
+        <v>54112.958519</v>
       </c>
       <c r="I94" t="n">
-        <v>51746.075764</v>
+        <v>51751.958481</v>
       </c>
       <c r="J94" t="n">
         <v>47765.953061</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>45338.619347</v>
+        <v>45215.794618</v>
       </c>
       <c r="F95" t="n">
-        <v>42861.70549</v>
+        <v>42808.729896</v>
       </c>
       <c r="G95" t="n">
-        <v>43037.6802</v>
+        <v>43010.791802</v>
       </c>
       <c r="H95" t="n">
-        <v>40706.888532</v>
+        <v>40694.415255</v>
       </c>
       <c r="I95" t="n">
-        <v>38004.989289</v>
+        <v>38000.354038</v>
       </c>
       <c r="J95" t="n">
         <v>34596.879735</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7139.634861</v>
+        <v>7205.735365</v>
       </c>
       <c r="F96" t="n">
-        <v>7824.377155</v>
+        <v>7854.027817</v>
       </c>
       <c r="G96" t="n">
-        <v>9187.98855</v>
+        <v>9202.952619</v>
       </c>
       <c r="H96" t="n">
-        <v>9639.575305</v>
+        <v>9646.526762</v>
       </c>
       <c r="I96" t="n">
-        <v>9562.890036000001</v>
+        <v>9565.565108999999</v>
       </c>
       <c r="J96" t="n">
         <v>8973.629709999999</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2383.726671</v>
+        <v>2388.891236</v>
       </c>
       <c r="F97" t="n">
-        <v>2822.331843</v>
+        <v>2822.2096</v>
       </c>
       <c r="G97" t="n">
-        <v>3425.23857</v>
+        <v>3423.632707</v>
       </c>
       <c r="H97" t="n">
-        <v>3650.227006</v>
+        <v>3648.823045</v>
       </c>
       <c r="I97" t="n">
-        <v>3661.576926</v>
+        <v>3660.883221</v>
       </c>
       <c r="J97" t="n">
         <v>3479.925348</v>
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>12644.36896</v>
+        <v>12662.371036</v>
       </c>
       <c r="F98" t="n">
-        <v>13565.983557</v>
+        <v>13573.966483</v>
       </c>
       <c r="G98" t="n">
-        <v>16132.276098</v>
+        <v>16136.44525</v>
       </c>
       <c r="H98" t="n">
-        <v>17351.729239</v>
+        <v>17353.360988</v>
       </c>
       <c r="I98" t="n">
-        <v>18584.689724</v>
+        <v>18584.78294</v>
       </c>
       <c r="J98" t="n">
-        <v>18564.756473</v>
+        <v>18563.983258</v>
       </c>
       <c r="K98" t="n">
-        <v>18166.551147</v>
+        <v>18165.367518</v>
       </c>
       <c r="L98" t="n">
-        <v>17671.043256</v>
+        <v>17669.723834</v>
       </c>
       <c r="M98" t="n">
-        <v>16751.199553</v>
+        <v>16749.909445</v>
       </c>
       <c r="N98" t="n">
-        <v>15313.914711</v>
+        <v>15312.751301</v>
       </c>
       <c r="O98" t="n">
-        <v>13541.528617</v>
+        <v>13540.533327</v>
       </c>
       <c r="P98" t="n">
-        <v>11551.064695</v>
+        <v>11550.251904</v>
       </c>
       <c r="Q98" t="n">
-        <v>9537.663299</v>
+        <v>9537.029130000001</v>
       </c>
       <c r="R98" t="n">
-        <v>7662.092755</v>
+        <v>7661.620449</v>
       </c>
       <c r="S98" t="n">
-        <v>6149.559092</v>
+        <v>6149.213508</v>
       </c>
       <c r="T98" t="n">
-        <v>5073.885117</v>
+        <v>5073.625778</v>
       </c>
       <c r="U98" t="n">
-        <v>4323.728327</v>
+        <v>4323.530636</v>
       </c>
       <c r="V98" t="n">
-        <v>3727.946841</v>
+        <v>3727.799188</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>16189.93603</v>
+        <v>16222.119749</v>
       </c>
       <c r="F99" t="n">
-        <v>14767.921786</v>
+        <v>14790.31216</v>
       </c>
       <c r="G99" t="n">
-        <v>14694.929235</v>
+        <v>14717.44141</v>
       </c>
       <c r="H99" t="n">
-        <v>13840.7297</v>
+        <v>13862.448434</v>
       </c>
       <c r="I99" t="n">
-        <v>13602.957419</v>
+        <v>13624.159656</v>
       </c>
       <c r="J99" t="n">
-        <v>12941.030153</v>
+        <v>12960.516787</v>
       </c>
       <c r="K99" t="n">
-        <v>12344.713996</v>
+        <v>12362.386727</v>
       </c>
       <c r="L99" t="n">
-        <v>11891.630136</v>
+        <v>11907.691878</v>
       </c>
       <c r="M99" t="n">
-        <v>11273.103208</v>
+        <v>11287.431321</v>
       </c>
       <c r="N99" t="n">
-        <v>10361.043417</v>
+        <v>10373.432145</v>
       </c>
       <c r="O99" t="n">
-        <v>9239.786925</v>
+        <v>9250.176310999999</v>
       </c>
       <c r="P99" t="n">
-        <v>7957.359059</v>
+        <v>7965.739985</v>
       </c>
       <c r="Q99" t="n">
-        <v>6637.893742</v>
+        <v>6644.396226</v>
       </c>
       <c r="R99" t="n">
-        <v>5395.616097</v>
+        <v>5400.48554</v>
       </c>
       <c r="S99" t="n">
-        <v>4385.474957</v>
+        <v>4389.074682</v>
       </c>
       <c r="T99" t="n">
-        <v>3660.9686</v>
+        <v>3663.653845</v>
       </c>
       <c r="U99" t="n">
-        <v>3155.35176</v>
+        <v>3157.369626</v>
       </c>
       <c r="V99" t="n">
-        <v>2746.909687</v>
+        <v>2748.389835</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>9718.342130000001</v>
+        <v>9715.300998000001</v>
       </c>
       <c r="F100" t="n">
-        <v>10649.710749</v>
+        <v>10646.39245</v>
       </c>
       <c r="G100" t="n">
-        <v>12634.676646</v>
+        <v>12630.364118</v>
       </c>
       <c r="H100" t="n">
-        <v>13548.072168</v>
+        <v>13543.199309</v>
       </c>
       <c r="I100" t="n">
-        <v>14517.272622</v>
+        <v>14511.961655</v>
       </c>
       <c r="J100" t="n">
-        <v>14569.007046</v>
+        <v>14563.727645</v>
       </c>
       <c r="K100" t="n">
-        <v>14354.233609</v>
+        <v>14349.166653</v>
       </c>
       <c r="L100" t="n">
-        <v>14109.350577</v>
+        <v>14104.552947</v>
       </c>
       <c r="M100" t="n">
-        <v>13563.574033</v>
+        <v>13559.156291</v>
       </c>
       <c r="N100" t="n">
-        <v>12604.001125</v>
+        <v>12600.083557</v>
       </c>
       <c r="O100" t="n">
-        <v>11356.233782</v>
+        <v>11352.874468</v>
       </c>
       <c r="P100" t="n">
-        <v>9872.132877</v>
+        <v>9869.370509</v>
       </c>
       <c r="Q100" t="n">
-        <v>8304.630950000001</v>
+        <v>8302.452240000001</v>
       </c>
       <c r="R100" t="n">
-        <v>6801.873908</v>
+        <v>6800.218044</v>
       </c>
       <c r="S100" t="n">
-        <v>5566.518948</v>
+        <v>5565.278432</v>
       </c>
       <c r="T100" t="n">
-        <v>4678.334895</v>
+        <v>4677.39601</v>
       </c>
       <c r="U100" t="n">
-        <v>4067.306196</v>
+        <v>4066.588217</v>
       </c>
       <c r="V100" t="n">
-        <v>3595.353248</v>
+        <v>3594.813385</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>9300.954492999999</v>
+        <v>9310.747020999999</v>
       </c>
       <c r="F101" t="n">
-        <v>9360.469302</v>
+        <v>9365.84446</v>
       </c>
       <c r="G101" t="n">
-        <v>10255.057169</v>
+        <v>10259.324944</v>
       </c>
       <c r="H101" t="n">
-        <v>10349.190591</v>
+        <v>10352.57533</v>
       </c>
       <c r="I101" t="n">
-        <v>10638.489549</v>
+        <v>10641.277397</v>
       </c>
       <c r="J101" t="n">
-        <v>10392.401184</v>
+        <v>10394.620983</v>
       </c>
       <c r="K101" t="n">
-        <v>10070.301895</v>
+        <v>10072.091678</v>
       </c>
       <c r="L101" t="n">
-        <v>9801.93548</v>
+        <v>9803.418905</v>
       </c>
       <c r="M101" t="n">
-        <v>9371.592817000001</v>
+        <v>9372.823004</v>
       </c>
       <c r="N101" t="n">
-        <v>8675.200800000001</v>
+        <v>8676.21055</v>
       </c>
       <c r="O101" t="n">
-        <v>7788.356093</v>
+        <v>7789.174628</v>
       </c>
       <c r="P101" t="n">
-        <v>6743.62188</v>
+        <v>6744.272697</v>
       </c>
       <c r="Q101" t="n">
-        <v>5649.479429</v>
+        <v>5649.984576</v>
       </c>
       <c r="R101" t="n">
-        <v>4608.059887</v>
+        <v>4608.441311</v>
       </c>
       <c r="S101" t="n">
-        <v>3762.314957</v>
+        <v>3762.597803</v>
       </c>
       <c r="T101" t="n">
-        <v>3160.291017</v>
+        <v>3160.500239</v>
       </c>
       <c r="U101" t="n">
-        <v>2743.928748</v>
+        <v>2744.084004</v>
       </c>
       <c r="V101" t="n">
-        <v>2412.247399</v>
+        <v>2412.359628</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>112628.563694</v>
+        <v>112593.318051</v>
       </c>
       <c r="F102" t="n">
-        <v>107956.226057</v>
+        <v>107941.337106</v>
       </c>
       <c r="G102" t="n">
-        <v>111284.713843</v>
+        <v>111277.740742</v>
       </c>
       <c r="H102" t="n">
-        <v>106727.103685</v>
+        <v>106725.381372</v>
       </c>
       <c r="I102" t="n">
-        <v>105666.283903</v>
+        <v>105667.594918</v>
       </c>
       <c r="J102" t="n">
-        <v>100725.410422</v>
+        <v>100728.246207</v>
       </c>
       <c r="K102" t="n">
-        <v>96111.499528</v>
+        <v>96114.910458</v>
       </c>
       <c r="L102" t="n">
-        <v>92656.66250200001</v>
+        <v>92660.178614</v>
       </c>
       <c r="M102" t="n">
-        <v>88135.153939</v>
+        <v>88138.39316599999</v>
       </c>
       <c r="N102" t="n">
-        <v>81500.37340300001</v>
+        <v>81503.12123600001</v>
       </c>
       <c r="O102" t="n">
-        <v>73332.53666300001</v>
+        <v>73334.723578</v>
       </c>
       <c r="P102" t="n">
-        <v>63795.720499</v>
+        <v>63797.397584</v>
       </c>
       <c r="Q102" t="n">
-        <v>53783.263378</v>
+        <v>53784.52005</v>
       </c>
       <c r="R102" t="n">
-        <v>44191.269482</v>
+        <v>44192.191893</v>
       </c>
       <c r="S102" t="n">
-        <v>36300.373907</v>
+        <v>36301.059896</v>
       </c>
       <c r="T102" t="n">
-        <v>30534.518444</v>
+        <v>30535.053118</v>
       </c>
       <c r="U102" t="n">
-        <v>26520.24546</v>
+        <v>26520.661072</v>
       </c>
       <c r="V102" t="n">
-        <v>23378.369987</v>
+        <v>23378.672296</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>147392.237629</v>
+        <v>147456.554499</v>
       </c>
       <c r="F103" t="n">
-        <v>158961.093684</v>
+        <v>158968.362957</v>
       </c>
       <c r="G103" t="n">
-        <v>188028.826694</v>
+        <v>188006.068815</v>
       </c>
       <c r="H103" t="n">
-        <v>199839.19673</v>
+        <v>199799.113502</v>
       </c>
       <c r="I103" t="n">
-        <v>210523.39438</v>
+        <v>210473.504271</v>
       </c>
       <c r="J103" t="n">
-        <v>206518.705336</v>
+        <v>206467.226417</v>
       </c>
       <c r="K103" t="n">
-        <v>197873.568924</v>
+        <v>197824.531562</v>
       </c>
       <c r="L103" t="n">
-        <v>188337.693331</v>
+        <v>188292.741545</v>
       </c>
       <c r="M103" t="n">
-        <v>174850.992395</v>
+        <v>174811.41766</v>
       </c>
       <c r="N103" t="n">
-        <v>157088.180672</v>
+        <v>157054.655739</v>
       </c>
       <c r="O103" t="n">
-        <v>137040.787816</v>
+        <v>137013.279273</v>
       </c>
       <c r="P103" t="n">
-        <v>115649.680527</v>
+        <v>115627.963637</v>
       </c>
       <c r="Q103" t="n">
-        <v>94572.525479</v>
+        <v>94556.080412</v>
       </c>
       <c r="R103" t="n">
-        <v>75263.386318</v>
+        <v>75251.433597</v>
       </c>
       <c r="S103" t="n">
-        <v>59873.644951</v>
+        <v>59865.08395</v>
       </c>
       <c r="T103" t="n">
-        <v>49017.196827</v>
+        <v>49010.965679</v>
       </c>
       <c r="U103" t="n">
-        <v>41587.215443</v>
+        <v>41582.602806</v>
       </c>
       <c r="V103" t="n">
-        <v>35653.316849</v>
+        <v>35649.994316</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>22461.714878</v>
+        <v>22452.864382</v>
       </c>
       <c r="F104" t="n">
-        <v>21169.748222</v>
+        <v>21165.390818</v>
       </c>
       <c r="G104" t="n">
-        <v>21694.128982</v>
+        <v>21690.90849</v>
       </c>
       <c r="H104" t="n">
-        <v>20370.839264</v>
+        <v>20368.721951</v>
       </c>
       <c r="I104" t="n">
-        <v>19592.419149</v>
+        <v>19591.097748</v>
       </c>
       <c r="J104" t="n">
-        <v>18097.554789</v>
+        <v>18096.848405</v>
       </c>
       <c r="K104" t="n">
-        <v>16773.490453</v>
+        <v>16773.150106</v>
       </c>
       <c r="L104" t="n">
-        <v>15766.940199</v>
+        <v>15766.771044</v>
       </c>
       <c r="M104" t="n">
-        <v>14639.82256</v>
+        <v>14639.715538</v>
       </c>
       <c r="N104" t="n">
-        <v>13213.017029</v>
+        <v>13212.926307</v>
       </c>
       <c r="O104" t="n">
-        <v>11576.399684</v>
+        <v>11576.316513</v>
       </c>
       <c r="P104" t="n">
-        <v>9800.155984999999</v>
+        <v>9800.079121000001</v>
       </c>
       <c r="Q104" t="n">
-        <v>8051.447428</v>
+        <v>8051.37273</v>
       </c>
       <c r="R104" t="n">
-        <v>6465.533842</v>
+        <v>6465.459847</v>
       </c>
       <c r="S104" t="n">
-        <v>5207.693078</v>
+        <v>5207.62243</v>
       </c>
       <c r="T104" t="n">
-        <v>4315.779465</v>
+        <v>4315.715952</v>
       </c>
       <c r="U104" t="n">
-        <v>3691.683561</v>
+        <v>3691.631418</v>
       </c>
       <c r="V104" t="n">
-        <v>3190.354401</v>
+        <v>3190.315517</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>7677.863844</v>
+        <v>7676.372951</v>
       </c>
       <c r="F105" t="n">
-        <v>7989.474421</v>
+        <v>7988.309756</v>
       </c>
       <c r="G105" t="n">
-        <v>8787.654164</v>
+        <v>8786.564017000001</v>
       </c>
       <c r="H105" t="n">
-        <v>8930.257489</v>
+        <v>8929.186632999999</v>
       </c>
       <c r="I105" t="n">
-        <v>9322.067244</v>
+        <v>9320.89963</v>
       </c>
       <c r="J105" t="n">
-        <v>9336.939934</v>
+        <v>9335.678532</v>
       </c>
       <c r="K105" t="n">
-        <v>9307.545751</v>
+        <v>9306.205204</v>
       </c>
       <c r="L105" t="n">
-        <v>9301.431028000001</v>
+        <v>9300.038968000001</v>
       </c>
       <c r="M105" t="n">
-        <v>9076.900528</v>
+        <v>9075.525197000001</v>
       </c>
       <c r="N105" t="n">
-        <v>8530.780054999999</v>
+        <v>8529.498962</v>
       </c>
       <c r="O105" t="n">
-        <v>7743.375772</v>
+        <v>7742.238774</v>
       </c>
       <c r="P105" t="n">
-        <v>6772.685619</v>
+        <v>6771.722099</v>
       </c>
       <c r="Q105" t="n">
-        <v>5737.204383</v>
+        <v>5736.418976</v>
       </c>
       <c r="R105" t="n">
-        <v>4742.248502</v>
+        <v>4741.627797</v>
       </c>
       <c r="S105" t="n">
-        <v>3924.892881</v>
+        <v>3924.407706</v>
       </c>
       <c r="T105" t="n">
-        <v>3336.447414</v>
+        <v>3336.065206</v>
       </c>
       <c r="U105" t="n">
-        <v>2925.867551</v>
+        <v>2925.566249</v>
       </c>
       <c r="V105" t="n">
-        <v>2597.777376</v>
+        <v>2597.545885</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>121833.570705</v>
+        <v>121762.555</v>
       </c>
       <c r="F106" t="n">
-        <v>109798.809402</v>
+        <v>109769.329792</v>
       </c>
       <c r="G106" t="n">
-        <v>105319.450186</v>
+        <v>105306.051645</v>
       </c>
       <c r="H106" t="n">
-        <v>95326.402391</v>
+        <v>95322.75182</v>
       </c>
       <c r="I106" t="n">
-        <v>90154.912513</v>
+        <v>90156.65964300001</v>
       </c>
       <c r="J106" t="n">
-        <v>82936.403981</v>
+        <v>82940.81544799999</v>
       </c>
       <c r="K106" t="n">
-        <v>76906.806126</v>
+        <v>76912.20032600001</v>
       </c>
       <c r="L106" t="n">
-        <v>72376.142532</v>
+        <v>72381.638009</v>
       </c>
       <c r="M106" t="n">
-        <v>67121.40411600001</v>
+        <v>67126.579278</v>
       </c>
       <c r="N106" t="n">
-        <v>60384.748698</v>
+        <v>60389.3593</v>
       </c>
       <c r="O106" t="n">
-        <v>52754.290038</v>
+        <v>52758.217886</v>
       </c>
       <c r="P106" t="n">
-        <v>44616.716784</v>
+        <v>44619.878846</v>
       </c>
       <c r="Q106" t="n">
-        <v>36695.826354</v>
+        <v>36698.228392</v>
       </c>
       <c r="R106" t="n">
-        <v>29537.017419</v>
+        <v>29538.753847</v>
       </c>
       <c r="S106" t="n">
-        <v>23835.487668</v>
+        <v>23836.736623</v>
       </c>
       <c r="T106" t="n">
-        <v>19709.591793</v>
+        <v>19710.531815</v>
       </c>
       <c r="U106" t="n">
-        <v>16771.832146</v>
+        <v>16772.569847</v>
       </c>
       <c r="V106" t="n">
-        <v>14464.172235</v>
+        <v>14464.734691</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>265.007084</v>
+        <v>267.050662</v>
       </c>
       <c r="F107" t="n">
-        <v>256.981377</v>
+        <v>258.341657</v>
       </c>
       <c r="G107" t="n">
-        <v>289.955535</v>
+        <v>291.199199</v>
       </c>
       <c r="H107" t="n">
-        <v>306.018876</v>
+        <v>307.146386</v>
       </c>
       <c r="I107" t="n">
-        <v>328.248443</v>
+        <v>329.322955</v>
       </c>
       <c r="J107" t="n">
-        <v>332.865748</v>
+        <v>333.857908</v>
       </c>
       <c r="K107" t="n">
-        <v>333.395943</v>
+        <v>334.314994</v>
       </c>
       <c r="L107" t="n">
-        <v>334.454365</v>
+        <v>335.313254</v>
       </c>
       <c r="M107" t="n">
-        <v>328.935226</v>
+        <v>329.723176</v>
       </c>
       <c r="N107" t="n">
-        <v>313.198215</v>
+        <v>313.895904</v>
       </c>
       <c r="O107" t="n">
-        <v>288.564589</v>
+        <v>289.160704</v>
       </c>
       <c r="P107" t="n">
-        <v>255.938628</v>
+        <v>256.426082</v>
       </c>
       <c r="Q107" t="n">
-        <v>219.18695</v>
+        <v>219.568525</v>
       </c>
       <c r="R107" t="n">
-        <v>182.402749</v>
+        <v>182.689916</v>
       </c>
       <c r="S107" t="n">
-        <v>151.465144</v>
+        <v>151.677729</v>
       </c>
       <c r="T107" t="n">
-        <v>129.000517</v>
+        <v>129.158817</v>
       </c>
       <c r="U107" t="n">
-        <v>113.268887</v>
+        <v>113.387314</v>
       </c>
       <c r="V107" t="n">
-        <v>100.425461</v>
+        <v>100.511732</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>21199.985968</v>
+        <v>21244.422444</v>
       </c>
       <c r="F108" t="n">
-        <v>20861.588559</v>
+        <v>20887.716133</v>
       </c>
       <c r="G108" t="n">
-        <v>22833.022021</v>
+        <v>22854.702481</v>
       </c>
       <c r="H108" t="n">
-        <v>23104.10578</v>
+        <v>23122.145299</v>
       </c>
       <c r="I108" t="n">
-        <v>23773.24486</v>
+        <v>23789.039535</v>
       </c>
       <c r="J108" t="n">
-        <v>23179.824886</v>
+        <v>23193.285673</v>
       </c>
       <c r="K108" t="n">
-        <v>22371.843395</v>
+        <v>22383.433564</v>
       </c>
       <c r="L108" t="n">
-        <v>21645.762117</v>
+        <v>21655.951487</v>
       </c>
       <c r="M108" t="n">
-        <v>20555.494459</v>
+        <v>20564.391243</v>
       </c>
       <c r="N108" t="n">
-        <v>18922.147762</v>
+        <v>18929.733823</v>
       </c>
       <c r="O108" t="n">
-        <v>16931.844715</v>
+        <v>16938.147494</v>
       </c>
       <c r="P108" t="n">
-        <v>14644.027676</v>
+        <v>14649.094113</v>
       </c>
       <c r="Q108" t="n">
-        <v>12274.442465</v>
+        <v>12278.383075</v>
       </c>
       <c r="R108" t="n">
-        <v>10020.240639</v>
+        <v>10023.219249</v>
       </c>
       <c r="S108" t="n">
-        <v>8172.868092</v>
+        <v>8175.10501</v>
       </c>
       <c r="T108" t="n">
-        <v>6847.831182</v>
+        <v>6849.529867</v>
       </c>
       <c r="U108" t="n">
-        <v>5939.789213</v>
+        <v>5941.084895</v>
       </c>
       <c r="V108" t="n">
-        <v>5219.953112</v>
+        <v>5220.915226</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>32267.899475</v>
+        <v>32240.351082</v>
       </c>
       <c r="F109" t="n">
-        <v>31173.409522</v>
+        <v>31157.718564</v>
       </c>
       <c r="G109" t="n">
-        <v>30943.706971</v>
+        <v>30932.068134</v>
       </c>
       <c r="H109" t="n">
-        <v>27656.258691</v>
+        <v>27648.471185</v>
       </c>
       <c r="I109" t="n">
-        <v>25152.934515</v>
+        <v>25148.055985</v>
       </c>
       <c r="J109" t="n">
-        <v>22208.642315</v>
+        <v>22205.970876</v>
       </c>
       <c r="K109" t="n">
-        <v>19942.424347</v>
+        <v>19941.114923</v>
       </c>
       <c r="L109" t="n">
-        <v>18379.090669</v>
+        <v>18378.542855</v>
       </c>
       <c r="M109" t="n">
-        <v>16884.221428</v>
+        <v>16884.074997</v>
       </c>
       <c r="N109" t="n">
-        <v>15177.697941</v>
+        <v>15177.741819</v>
       </c>
       <c r="O109" t="n">
-        <v>13305.406122</v>
+        <v>13305.52677</v>
       </c>
       <c r="P109" t="n">
-        <v>11295.351235</v>
+        <v>11295.488183</v>
       </c>
       <c r="Q109" t="n">
-        <v>9310.241293999999</v>
+        <v>9310.361524</v>
       </c>
       <c r="R109" t="n">
-        <v>7504.257967</v>
+        <v>7504.345554</v>
       </c>
       <c r="S109" t="n">
-        <v>6069.116745</v>
+        <v>6069.17447</v>
       </c>
       <c r="T109" t="n">
-        <v>5050.767422</v>
+        <v>5050.805092</v>
       </c>
       <c r="U109" t="n">
-        <v>4344.149865</v>
+        <v>4344.176291</v>
       </c>
       <c r="V109" t="n">
-        <v>3782.18863</v>
+        <v>3782.207734</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>14257.41449</v>
+        <v>14261.173519</v>
       </c>
       <c r="F110" t="n">
-        <v>13625.827533</v>
+        <v>13629.354503</v>
       </c>
       <c r="G110" t="n">
-        <v>14052.628726</v>
+        <v>14056.986203</v>
       </c>
       <c r="H110" t="n">
-        <v>13603.327707</v>
+        <v>13607.939081</v>
       </c>
       <c r="I110" t="n">
-        <v>13712.500437</v>
+        <v>13717.096071</v>
       </c>
       <c r="J110" t="n">
-        <v>13376.205985</v>
+        <v>13380.381631</v>
       </c>
       <c r="K110" t="n">
-        <v>13103.775508</v>
+        <v>13107.466402</v>
       </c>
       <c r="L110" t="n">
-        <v>12967.330807</v>
+        <v>12970.596824</v>
       </c>
       <c r="M110" t="n">
-        <v>12613.961113</v>
+        <v>12616.810049</v>
       </c>
       <c r="N110" t="n">
-        <v>11863.185624</v>
+        <v>11865.618196</v>
       </c>
       <c r="O110" t="n">
-        <v>10789.788153</v>
+        <v>10791.821898</v>
       </c>
       <c r="P110" t="n">
-        <v>9457.438875</v>
+        <v>9459.084322999999</v>
       </c>
       <c r="Q110" t="n">
-        <v>8022.058217</v>
+        <v>8023.341401</v>
       </c>
       <c r="R110" t="n">
-        <v>6627.518271</v>
+        <v>6628.482696</v>
       </c>
       <c r="S110" t="n">
-        <v>5472.098455</v>
+        <v>5472.811764</v>
       </c>
       <c r="T110" t="n">
-        <v>4639.063959</v>
+        <v>4639.592897</v>
       </c>
       <c r="U110" t="n">
-        <v>4063.253073</v>
+        <v>4063.644946</v>
       </c>
       <c r="V110" t="n">
-        <v>3600.385244</v>
+        <v>3600.667494</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>92701.586456</v>
+        <v>92680.489904</v>
       </c>
       <c r="F111" t="n">
-        <v>88497.52568200001</v>
+        <v>88489.670018</v>
       </c>
       <c r="G111" t="n">
-        <v>92325.789882</v>
+        <v>92321.44962699999</v>
       </c>
       <c r="H111" t="n">
-        <v>89846.269501</v>
+        <v>89843.623171</v>
       </c>
       <c r="I111" t="n">
-        <v>89833.51624500001</v>
+        <v>89831.783923</v>
       </c>
       <c r="J111" t="n">
-        <v>86183.298304</v>
+        <v>86182.09355999999</v>
       </c>
       <c r="K111" t="n">
-        <v>82676.63902800001</v>
+        <v>82675.484196</v>
       </c>
       <c r="L111" t="n">
-        <v>80107.231075</v>
+        <v>80105.73125899999</v>
       </c>
       <c r="M111" t="n">
-        <v>76205.404077</v>
+        <v>76203.57367500001</v>
       </c>
       <c r="N111" t="n">
-        <v>70078.318533</v>
+        <v>70076.358756</v>
       </c>
       <c r="O111" t="n">
-        <v>62341.769004</v>
+        <v>62339.883937</v>
       </c>
       <c r="P111" t="n">
-        <v>53550.923655</v>
+        <v>53549.195976</v>
       </c>
       <c r="Q111" t="n">
-        <v>44674.682829</v>
+        <v>44673.113428</v>
       </c>
       <c r="R111" t="n">
-        <v>36480.605651</v>
+        <v>36479.180917</v>
       </c>
       <c r="S111" t="n">
-        <v>29934.981469</v>
+        <v>29933.696706</v>
       </c>
       <c r="T111" t="n">
-        <v>25212.004791</v>
+        <v>25210.890185</v>
       </c>
       <c r="U111" t="n">
-        <v>21834.285099</v>
+        <v>21833.371152</v>
       </c>
       <c r="V111" t="n">
-        <v>19114.849158</v>
+        <v>19114.136261</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100644.891986</v>
+        <v>100638.646524</v>
       </c>
       <c r="F112" t="n">
-        <v>96266.166608</v>
+        <v>96268.889607</v>
       </c>
       <c r="G112" t="n">
-        <v>98584.376088</v>
+        <v>98593.87716600001</v>
       </c>
       <c r="H112" t="n">
-        <v>94103.20411999999</v>
+        <v>94116.641468</v>
       </c>
       <c r="I112" t="n">
-        <v>92883.137376</v>
+        <v>92898.832052</v>
       </c>
       <c r="J112" t="n">
-        <v>88489.999383</v>
+        <v>88505.792612</v>
       </c>
       <c r="K112" t="n">
-        <v>84653.972836</v>
+        <v>84668.938175</v>
       </c>
       <c r="L112" t="n">
-        <v>82003.27467300001</v>
+        <v>82017.081324</v>
       </c>
       <c r="M112" t="n">
-        <v>78377.96655</v>
+        <v>78390.201963</v>
       </c>
       <c r="N112" t="n">
-        <v>72689.776287</v>
+        <v>72700.196677</v>
       </c>
       <c r="O112" t="n">
-        <v>65460.085229</v>
+        <v>65468.677639</v>
       </c>
       <c r="P112" t="n">
-        <v>56934.782371</v>
+        <v>56941.635308</v>
       </c>
       <c r="Q112" t="n">
-        <v>47971.473168</v>
+        <v>47976.76868</v>
       </c>
       <c r="R112" t="n">
-        <v>39385.895001</v>
+        <v>39389.867829</v>
       </c>
       <c r="S112" t="n">
-        <v>32346.242697</v>
+        <v>32349.192331</v>
       </c>
       <c r="T112" t="n">
-        <v>27322.456731</v>
+        <v>27324.653675</v>
       </c>
       <c r="U112" t="n">
-        <v>23891.300895</v>
+        <v>23892.93775</v>
       </c>
       <c r="V112" t="n">
-        <v>21201.31054</v>
+        <v>21202.496982</v>
       </c>
     </row>
     <row r="113">
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13431.633348</v>
+        <v>13769.779132</v>
       </c>
       <c r="F113" t="n">
-        <v>15632.615357</v>
+        <v>15717.345498</v>
       </c>
       <c r="G113" t="n">
-        <v>14539.431172</v>
+        <v>14258.822158</v>
       </c>
       <c r="H113" t="n">
-        <v>14151.411457</v>
+        <v>13663.807628</v>
       </c>
       <c r="I113" t="n">
-        <v>13251.197348</v>
+        <v>12714.511868</v>
       </c>
       <c r="J113" t="n">
-        <v>12464.130907</v>
+        <v>11957.85677</v>
       </c>
       <c r="K113" t="n">
-        <v>11581.757145</v>
+        <v>11140.860012</v>
       </c>
       <c r="L113" t="n">
-        <v>10517.108558</v>
+        <v>10152.83301</v>
       </c>
       <c r="M113" t="n">
-        <v>9395.520791000001</v>
+        <v>9101.722612</v>
       </c>
       <c r="N113" t="n">
-        <v>8300.352502</v>
+        <v>8065.303311</v>
       </c>
       <c r="O113" t="n">
-        <v>7334.144264</v>
+        <v>7144.20683</v>
       </c>
       <c r="P113" t="n">
-        <v>6393.174575</v>
+        <v>6240.78782</v>
       </c>
       <c r="Q113" t="n">
-        <v>5513.65771</v>
+        <v>5392.555423</v>
       </c>
       <c r="R113" t="n">
-        <v>4720.265265</v>
+        <v>4625.129222</v>
       </c>
       <c r="S113" t="n">
-        <v>4024.400414</v>
+        <v>3950.704931</v>
       </c>
       <c r="T113" t="n">
-        <v>3429.619398</v>
+        <v>3373.416873</v>
       </c>
       <c r="U113" t="n">
-        <v>2917.249033</v>
+        <v>2875.437825</v>
       </c>
       <c r="V113" t="n">
-        <v>2455.821061</v>
+        <v>2426.128303</v>
       </c>
     </row>
     <row r="114">
@@ -9038,58 +9038,58 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>7576.623149</v>
+        <v>6855.628161</v>
       </c>
       <c r="F114" t="n">
-        <v>7929.076124</v>
+        <v>7327.800904</v>
       </c>
       <c r="G114" t="n">
-        <v>6156.084447</v>
+        <v>5759.457277</v>
       </c>
       <c r="H114" t="n">
-        <v>5215.255615</v>
+        <v>4937.881896</v>
       </c>
       <c r="I114" t="n">
-        <v>4407.774245</v>
+        <v>4212.526099</v>
       </c>
       <c r="J114" t="n">
-        <v>3837.686118</v>
+        <v>3691.576191</v>
       </c>
       <c r="K114" t="n">
-        <v>3353.102055</v>
+        <v>3240.31984</v>
       </c>
       <c r="L114" t="n">
-        <v>2891.47996</v>
+        <v>2804.069491</v>
       </c>
       <c r="M114" t="n">
-        <v>2463.498613</v>
+        <v>2396.049835</v>
       </c>
       <c r="N114" t="n">
-        <v>2077.148108</v>
+        <v>2025.312954</v>
       </c>
       <c r="O114" t="n">
-        <v>1756.148918</v>
+        <v>1715.836053</v>
       </c>
       <c r="P114" t="n">
-        <v>1465.048172</v>
+        <v>1434.062586</v>
       </c>
       <c r="Q114" t="n">
-        <v>1208.808076</v>
+        <v>1185.310853</v>
       </c>
       <c r="R114" t="n">
-        <v>991.523958</v>
+        <v>973.890183</v>
       </c>
       <c r="S114" t="n">
-        <v>812.970148</v>
+        <v>799.852636</v>
       </c>
       <c r="T114" t="n">
-        <v>669.7491</v>
+        <v>660.077797</v>
       </c>
       <c r="U114" t="n">
-        <v>554.229933</v>
+        <v>547.2213829999999</v>
       </c>
       <c r="V114" t="n">
-        <v>456.679021</v>
+        <v>451.80312</v>
       </c>
     </row>
     <row r="115">
@@ -9114,58 +9114,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>87375.3239</v>
+        <v>87758.173104</v>
       </c>
       <c r="F115" t="n">
-        <v>100476.736532</v>
+        <v>100993.28161</v>
       </c>
       <c r="G115" t="n">
-        <v>89455.679562</v>
+        <v>90132.91574700001</v>
       </c>
       <c r="H115" t="n">
-        <v>83069.47698599999</v>
+        <v>83834.454535</v>
       </c>
       <c r="I115" t="n">
-        <v>74590.459474</v>
+        <v>75322.39310099999</v>
       </c>
       <c r="J115" t="n">
-        <v>68086.182764</v>
+        <v>68738.566828</v>
       </c>
       <c r="K115" t="n">
-        <v>62178.897162</v>
+        <v>62732.57651</v>
       </c>
       <c r="L115" t="n">
-        <v>56057.883307</v>
+        <v>56509.569323</v>
       </c>
       <c r="M115" t="n">
-        <v>50066.794324</v>
+        <v>50428.04128</v>
       </c>
       <c r="N115" t="n">
-        <v>44434.645079</v>
+        <v>44721.529424</v>
       </c>
       <c r="O115" t="n">
-        <v>39461.4672</v>
+        <v>39691.717498</v>
       </c>
       <c r="P115" t="n">
-        <v>34576.248902</v>
+        <v>34759.621242</v>
       </c>
       <c r="Q115" t="n">
-        <v>29973.71375</v>
+        <v>30118.313259</v>
       </c>
       <c r="R115" t="n">
-        <v>25783.173508</v>
+        <v>25895.943325</v>
       </c>
       <c r="S115" t="n">
-        <v>22068.117849</v>
+        <v>22154.930845</v>
       </c>
       <c r="T115" t="n">
-        <v>18840.17255</v>
+        <v>18906.046378</v>
       </c>
       <c r="U115" t="n">
-        <v>16010.998671</v>
+        <v>16059.818429</v>
       </c>
       <c r="V115" t="n">
-        <v>13433.243128</v>
+        <v>13467.811788</v>
       </c>
     </row>
     <row r="116">
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>9837.201793</v>
+        <v>9800.466936000001</v>
       </c>
       <c r="F116" t="n">
-        <v>10344.704687</v>
+        <v>10326.051475</v>
       </c>
       <c r="G116" t="n">
-        <v>10258.954902</v>
+        <v>10248.127176</v>
       </c>
       <c r="H116" t="n">
-        <v>10112.105412</v>
+        <v>10106.080428</v>
       </c>
       <c r="I116" t="n">
-        <v>9782.606817</v>
+        <v>9780.02101</v>
       </c>
       <c r="J116" t="n">
         <v>9261.123548</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5147.581053</v>
+        <v>5145.545199</v>
       </c>
       <c r="F117" t="n">
-        <v>4383.840195</v>
+        <v>4387.825715</v>
       </c>
       <c r="G117" t="n">
-        <v>3881.897053</v>
+        <v>3885.784918</v>
       </c>
       <c r="H117" t="n">
-        <v>3565.851952</v>
+        <v>3568.522651</v>
       </c>
       <c r="I117" t="n">
-        <v>3290.771994</v>
+        <v>3292.029254</v>
       </c>
       <c r="J117" t="n">
         <v>3006.872624</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3729.010589</v>
+        <v>3741.731853</v>
       </c>
       <c r="F118" t="n">
-        <v>3843.895196</v>
+        <v>3850.334019</v>
       </c>
       <c r="G118" t="n">
-        <v>3793.315811</v>
+        <v>3796.964302</v>
       </c>
       <c r="H118" t="n">
-        <v>3734.535949</v>
+        <v>3736.505685</v>
       </c>
       <c r="I118" t="n">
-        <v>3610.418256</v>
+        <v>3611.234436</v>
       </c>
       <c r="J118" t="n">
         <v>3418.755273</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3000.636652</v>
+        <v>2995.929265</v>
       </c>
       <c r="F119" t="n">
-        <v>2770.748161</v>
+        <v>2770.095243</v>
       </c>
       <c r="G119" t="n">
-        <v>2475.961265</v>
+        <v>2476.489741</v>
       </c>
       <c r="H119" t="n">
-        <v>2280.052702</v>
+        <v>2280.733768</v>
       </c>
       <c r="I119" t="n">
-        <v>2129.678551</v>
+        <v>2130.081406</v>
       </c>
       <c r="J119" t="n">
         <v>1993.189929</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>810.7675</v>
+        <v>807.031713</v>
       </c>
       <c r="F120" t="n">
-        <v>859.121325</v>
+        <v>857.205492</v>
       </c>
       <c r="G120" t="n">
-        <v>859.809254</v>
+        <v>858.682959</v>
       </c>
       <c r="H120" t="n">
-        <v>857.169274</v>
+        <v>856.533866</v>
       </c>
       <c r="I120" t="n">
-        <v>840.208482</v>
+        <v>839.9319850000001</v>
       </c>
       <c r="J120" t="n">
         <v>807.205375</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>12755.313431</v>
+        <v>12696.540573</v>
       </c>
       <c r="F121" t="n">
-        <v>11518.603679</v>
+        <v>11492.917303</v>
       </c>
       <c r="G121" t="n">
-        <v>10131.474084</v>
+        <v>10118.2025</v>
       </c>
       <c r="H121" t="n">
-        <v>9290.773214999999</v>
+        <v>9283.88609</v>
       </c>
       <c r="I121" t="n">
-        <v>8683.960561</v>
+        <v>8681.102831</v>
       </c>
       <c r="J121" t="n">
         <v>8144.868985</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100902.236131</v>
+        <v>100995.501609</v>
       </c>
       <c r="F122" t="n">
-        <v>113599.280728</v>
+        <v>113635.764722</v>
       </c>
       <c r="G122" t="n">
-        <v>119732.833132</v>
+        <v>119749.993905</v>
       </c>
       <c r="H122" t="n">
-        <v>124069.33748</v>
+        <v>124077.563496</v>
       </c>
       <c r="I122" t="n">
-        <v>124964.737881</v>
+        <v>124967.98162</v>
       </c>
       <c r="J122" t="n">
         <v>122265.974884</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>945.625448</v>
+        <v>945.788664</v>
       </c>
       <c r="F123" t="n">
-        <v>973.195704</v>
+        <v>973.277976</v>
       </c>
       <c r="G123" t="n">
-        <v>996.828223</v>
+        <v>996.887346</v>
       </c>
       <c r="H123" t="n">
-        <v>986.241675</v>
+        <v>986.27982</v>
       </c>
       <c r="I123" t="n">
-        <v>1054.619535</v>
+        <v>1054.639725</v>
       </c>
       <c r="J123" t="n">
         <v>1039.650503</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>9529.921746</v>
+        <v>9532.802003000001</v>
       </c>
       <c r="F124" t="n">
-        <v>9463.473781000001</v>
+        <v>9464.964754000001</v>
       </c>
       <c r="G124" t="n">
-        <v>9662.547844999999</v>
+        <v>9663.567246000001</v>
       </c>
       <c r="H124" t="n">
-        <v>9552.50979</v>
+        <v>9553.148648</v>
       </c>
       <c r="I124" t="n">
-        <v>10261.907459</v>
+        <v>10262.236208</v>
       </c>
       <c r="J124" t="n">
         <v>10144.787617</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>20304.103107</v>
+        <v>20301.059634</v>
       </c>
       <c r="F125" t="n">
-        <v>21090.43516</v>
+        <v>21088.861916</v>
       </c>
       <c r="G125" t="n">
-        <v>22901.968703</v>
+        <v>22900.890179</v>
       </c>
       <c r="H125" t="n">
-        <v>23500.143467</v>
+        <v>23499.466464</v>
       </c>
       <c r="I125" t="n">
-        <v>25520.674289</v>
+        <v>25520.325351</v>
       </c>
       <c r="J125" t="n">
         <v>24987.395983</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5850.89456</v>
+        <v>6292.064391</v>
       </c>
       <c r="F130" t="n">
-        <v>6866.797984</v>
+        <v>7125.863807</v>
       </c>
       <c r="G130" t="n">
-        <v>8176.397702</v>
+        <v>8354.978662</v>
       </c>
       <c r="H130" t="n">
-        <v>9207.001385</v>
+        <v>9322.430877999999</v>
       </c>
       <c r="I130" t="n">
-        <v>10360.419193</v>
+        <v>10419.397867</v>
       </c>
       <c r="J130" t="n">
         <v>11116.881934</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1502.759909</v>
+        <v>1535.857769</v>
       </c>
       <c r="F131" t="n">
-        <v>1748.859643</v>
+        <v>1771.588941</v>
       </c>
       <c r="G131" t="n">
-        <v>2141.310876</v>
+        <v>2157.39897</v>
       </c>
       <c r="H131" t="n">
-        <v>2504.943039</v>
+        <v>2515.310333</v>
       </c>
       <c r="I131" t="n">
-        <v>2936.379057</v>
+        <v>2941.629417</v>
       </c>
       <c r="J131" t="n">
         <v>3272.928677</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>143256.48174</v>
+        <v>143323.553828</v>
       </c>
       <c r="F132" t="n">
-        <v>171505.343812</v>
+        <v>171485.550981</v>
       </c>
       <c r="G132" t="n">
-        <v>205539.528687</v>
+        <v>205481.974072</v>
       </c>
       <c r="H132" t="n">
-        <v>232690.796353</v>
+        <v>232636.007957</v>
       </c>
       <c r="I132" t="n">
-        <v>261716.992001</v>
+        <v>261684.160161</v>
       </c>
       <c r="J132" t="n">
         <v>277813.649616</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>118088.40304</v>
+        <v>117662.325252</v>
       </c>
       <c r="F133" t="n">
-        <v>125540.264071</v>
+        <v>125369.497805</v>
       </c>
       <c r="G133" t="n">
-        <v>137741.670446</v>
+        <v>137672.722447</v>
       </c>
       <c r="H133" t="n">
-        <v>154541.992104</v>
+        <v>154516.424741</v>
       </c>
       <c r="I133" t="n">
-        <v>182032.476322</v>
+        <v>182022.961445</v>
       </c>
       <c r="J133" t="n">
         <v>210302.343622</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>8050.825296</v>
+        <v>8050.340056</v>
       </c>
       <c r="F134" t="n">
-        <v>11138.867849</v>
+        <v>11129.708247</v>
       </c>
       <c r="G134" t="n">
-        <v>14852.699722</v>
+        <v>14841.333089</v>
       </c>
       <c r="H134" t="n">
-        <v>18105.649771</v>
+        <v>18096.480787</v>
       </c>
       <c r="I134" t="n">
-        <v>21547.698328</v>
+        <v>21542.542612</v>
       </c>
       <c r="J134" t="n">
         <v>24046.072002</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>24635.971021</v>
+        <v>24512.760975</v>
       </c>
       <c r="F135" t="n">
-        <v>28187.582381</v>
+        <v>28118.212103</v>
       </c>
       <c r="G135" t="n">
-        <v>32196.854113</v>
+        <v>32151.711595</v>
       </c>
       <c r="H135" t="n">
-        <v>36313.409589</v>
+        <v>36285.545957</v>
       </c>
       <c r="I135" t="n">
-        <v>41815.494233</v>
+        <v>41801.646987</v>
       </c>
       <c r="J135" t="n">
         <v>46304.066219</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2149.014416</v>
+        <v>2287.592452</v>
       </c>
       <c r="F136" t="n">
-        <v>2800.691059</v>
+        <v>2869.718552</v>
       </c>
       <c r="G136" t="n">
-        <v>3952.210231</v>
+        <v>3989.3885</v>
       </c>
       <c r="H136" t="n">
-        <v>5340.735652</v>
+        <v>5359.055268</v>
       </c>
       <c r="I136" t="n">
-        <v>6967.317303</v>
+        <v>6974.746826</v>
       </c>
       <c r="J136" t="n">
         <v>8029.401092</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6315.134265</v>
+        <v>6294.083717</v>
       </c>
       <c r="F137" t="n">
-        <v>7143.611882</v>
+        <v>7131.311596</v>
       </c>
       <c r="G137" t="n">
-        <v>8447.675718</v>
+        <v>8438.371485</v>
       </c>
       <c r="H137" t="n">
-        <v>9516.405761</v>
+        <v>9510.177443</v>
       </c>
       <c r="I137" t="n">
-        <v>10502.900086</v>
+        <v>10499.811588</v>
       </c>
       <c r="J137" t="n">
         <v>10821.125427</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3558.496643</v>
+        <v>3698.765335</v>
       </c>
       <c r="F138" t="n">
-        <v>4265.81378</v>
+        <v>4340.894374</v>
       </c>
       <c r="G138" t="n">
-        <v>5343.478337</v>
+        <v>5388.68994</v>
       </c>
       <c r="H138" t="n">
-        <v>6445.482692</v>
+        <v>6470.395598</v>
       </c>
       <c r="I138" t="n">
-        <v>7791.451457</v>
+        <v>7802.25529</v>
       </c>
       <c r="J138" t="n">
         <v>8882.564872000001</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5062.048944</v>
+        <v>5398.734015</v>
       </c>
       <c r="F139" t="n">
-        <v>5882.504565</v>
+        <v>6075.87916</v>
       </c>
       <c r="G139" t="n">
-        <v>6951.29811</v>
+        <v>7082.887879</v>
       </c>
       <c r="H139" t="n">
-        <v>7796.007473</v>
+        <v>7880.488551</v>
       </c>
       <c r="I139" t="n">
-        <v>8752.634980999999</v>
+        <v>8795.623679</v>
       </c>
       <c r="J139" t="n">
         <v>9361.931817000001</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>36448.185132</v>
+        <v>37257.777638</v>
       </c>
       <c r="F140" t="n">
-        <v>50210.360856</v>
+        <v>50598.785263</v>
       </c>
       <c r="G140" t="n">
-        <v>68177.892364</v>
+        <v>68398.267924</v>
       </c>
       <c r="H140" t="n">
-        <v>84884.35180600001</v>
+        <v>85010.490106</v>
       </c>
       <c r="I140" t="n">
-        <v>101806.523495</v>
+        <v>101869.155384</v>
       </c>
       <c r="J140" t="n">
         <v>113474.620716</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>95303.44942800001</v>
+        <v>94775.154729</v>
       </c>
       <c r="F141" t="n">
-        <v>116968.864152</v>
+        <v>116639.033735</v>
       </c>
       <c r="G141" t="n">
-        <v>143013.585641</v>
+        <v>142774.908212</v>
       </c>
       <c r="H141" t="n">
-        <v>167086.414047</v>
+        <v>166929.286702</v>
       </c>
       <c r="I141" t="n">
-        <v>194164.301204</v>
+        <v>194083.908259</v>
       </c>
       <c r="J141" t="n">
         <v>214273.031915</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>153318.122084</v>
+        <v>152450.776323</v>
       </c>
       <c r="F142" t="n">
-        <v>141285.632333</v>
+        <v>140889.149803</v>
       </c>
       <c r="G142" t="n">
-        <v>126007.956473</v>
+        <v>125809.925645</v>
       </c>
       <c r="H142" t="n">
-        <v>120291.489948</v>
+        <v>120192.585296</v>
       </c>
       <c r="I142" t="n">
-        <v>127640.381394</v>
+        <v>127597.129542</v>
       </c>
       <c r="J142" t="n">
         <v>139774.341809</v>
@@ -11470,58 +11470,58 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2365.126873</v>
+        <v>2318.003432</v>
       </c>
       <c r="F146" t="n">
-        <v>2811.718084</v>
+        <v>2772.436623</v>
       </c>
       <c r="G146" t="n">
-        <v>3272.486044</v>
+        <v>3232.067203</v>
       </c>
       <c r="H146" t="n">
-        <v>3354.909731</v>
+        <v>3317.772815</v>
       </c>
       <c r="I146" t="n">
-        <v>3123.300202</v>
+        <v>3092.954413</v>
       </c>
       <c r="J146" t="n">
-        <v>2758.442879</v>
+        <v>2735.263295</v>
       </c>
       <c r="K146" t="n">
-        <v>2446.17017</v>
+        <v>2428.47712</v>
       </c>
       <c r="L146" t="n">
-        <v>2141.13676</v>
+        <v>2127.877279</v>
       </c>
       <c r="M146" t="n">
-        <v>1827.320769</v>
+        <v>1817.651906</v>
       </c>
       <c r="N146" t="n">
-        <v>1525.093016</v>
+        <v>1518.150658</v>
       </c>
       <c r="O146" t="n">
-        <v>1241.074859</v>
+        <v>1236.171422</v>
       </c>
       <c r="P146" t="n">
-        <v>979.254506</v>
+        <v>975.885104</v>
       </c>
       <c r="Q146" t="n">
-        <v>762.35504</v>
+        <v>760.079252</v>
       </c>
       <c r="R146" t="n">
-        <v>596.395586</v>
+        <v>594.860503</v>
       </c>
       <c r="S146" t="n">
-        <v>472.084094</v>
+        <v>471.0481</v>
       </c>
       <c r="T146" t="n">
-        <v>374.25147</v>
+        <v>373.562061</v>
       </c>
       <c r="U146" t="n">
-        <v>298.672582</v>
+        <v>298.22071</v>
       </c>
       <c r="V146" t="n">
-        <v>242.42564</v>
+        <v>242.134937</v>
       </c>
     </row>
     <row r="147">
@@ -11546,58 +11546,58 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>642.3583159999999</v>
+        <v>630.361601</v>
       </c>
       <c r="F147" t="n">
-        <v>701.310389</v>
+        <v>692.222978</v>
       </c>
       <c r="G147" t="n">
-        <v>770.089834</v>
+        <v>761.278552</v>
       </c>
       <c r="H147" t="n">
-        <v>797.04738</v>
+        <v>788.841858</v>
       </c>
       <c r="I147" t="n">
-        <v>783.572769</v>
+        <v>776.464458</v>
       </c>
       <c r="J147" t="n">
-        <v>748.33496</v>
+        <v>742.44354</v>
       </c>
       <c r="K147" t="n">
-        <v>717.814087</v>
+        <v>712.9400429999999</v>
       </c>
       <c r="L147" t="n">
-        <v>682.458601</v>
+        <v>678.481169</v>
       </c>
       <c r="M147" t="n">
-        <v>634.48203</v>
+        <v>631.311273</v>
       </c>
       <c r="N147" t="n">
-        <v>577.858642</v>
+        <v>575.36179</v>
       </c>
       <c r="O147" t="n">
-        <v>511.555095</v>
+        <v>509.623798</v>
       </c>
       <c r="P147" t="n">
-        <v>438.608111</v>
+        <v>437.153947</v>
       </c>
       <c r="Q147" t="n">
-        <v>370.527483</v>
+        <v>369.451357</v>
       </c>
       <c r="R147" t="n">
-        <v>313.726911</v>
+        <v>312.932789</v>
       </c>
       <c r="S147" t="n">
-        <v>267.987977</v>
+        <v>267.402731</v>
       </c>
       <c r="T147" t="n">
-        <v>228.358729</v>
+        <v>227.934705</v>
       </c>
       <c r="U147" t="n">
-        <v>194.334181</v>
+        <v>194.03392</v>
       </c>
       <c r="V147" t="n">
-        <v>166.405017</v>
+        <v>166.198616</v>
       </c>
     </row>
     <row r="148">
@@ -11622,58 +11622,58 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>49360.061015</v>
+        <v>49419.18117</v>
       </c>
       <c r="F148" t="n">
-        <v>53841.819684</v>
+        <v>53890.188555</v>
       </c>
       <c r="G148" t="n">
-        <v>57856.023719</v>
+        <v>57905.253842</v>
       </c>
       <c r="H148" t="n">
-        <v>58827.333606</v>
+        <v>58872.676043</v>
       </c>
       <c r="I148" t="n">
-        <v>57766.599661</v>
+        <v>57804.053762</v>
       </c>
       <c r="J148" t="n">
-        <v>55830.945918</v>
+        <v>55860.016921</v>
       </c>
       <c r="K148" t="n">
-        <v>54774.304947</v>
+        <v>54796.872041</v>
       </c>
       <c r="L148" t="n">
-        <v>53348.690328</v>
+        <v>53365.927241</v>
       </c>
       <c r="M148" t="n">
-        <v>50719.815765</v>
+        <v>50732.655386</v>
       </c>
       <c r="N148" t="n">
-        <v>46999.948287</v>
+        <v>47009.387495</v>
       </c>
       <c r="O148" t="n">
-        <v>41988.84646</v>
+        <v>41995.681195</v>
       </c>
       <c r="P148" t="n">
-        <v>36092.964303</v>
+        <v>36097.787869</v>
       </c>
       <c r="Q148" t="n">
-        <v>30487.588182</v>
+        <v>30490.940097</v>
       </c>
       <c r="R148" t="n">
-        <v>25774.247182</v>
+        <v>25776.576386</v>
       </c>
       <c r="S148" t="n">
-        <v>21947.10392</v>
+        <v>21948.725161</v>
       </c>
       <c r="T148" t="n">
-        <v>18605.539616</v>
+        <v>18606.653048</v>
       </c>
       <c r="U148" t="n">
-        <v>15729.21075</v>
+        <v>15729.962882</v>
       </c>
       <c r="V148" t="n">
-        <v>13374.183834</v>
+        <v>13374.680938</v>
       </c>
     </row>
     <row r="149">
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>10397.892015</v>
+        <v>10198.631585</v>
       </c>
       <c r="F149" t="n">
-        <v>13032.108538</v>
+        <v>12900.002803</v>
       </c>
       <c r="G149" t="n">
-        <v>15860.71807</v>
+        <v>15767.45808</v>
       </c>
       <c r="H149" t="n">
-        <v>18450.689939</v>
+        <v>18392.423064</v>
       </c>
       <c r="I149" t="n">
-        <v>21130.975658</v>
+        <v>21103.054012</v>
       </c>
       <c r="J149" t="n">
         <v>22709.150671</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>9316.712788999999</v>
+        <v>9769.078948</v>
       </c>
       <c r="F150" t="n">
-        <v>10338.615304</v>
+        <v>10583.580308</v>
       </c>
       <c r="G150" t="n">
-        <v>11472.58051</v>
+        <v>11626.424827</v>
       </c>
       <c r="H150" t="n">
-        <v>12476.262312</v>
+        <v>12568.186298</v>
       </c>
       <c r="I150" t="n">
-        <v>13540.827682</v>
+        <v>13585.883593</v>
       </c>
       <c r="J150" t="n">
         <v>13826.10918</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>10972.396269</v>
+        <v>10947.513852</v>
       </c>
       <c r="F151" t="n">
-        <v>12829.273281</v>
+        <v>12813.405905</v>
       </c>
       <c r="G151" t="n">
-        <v>14564.834713</v>
+        <v>14558.825974</v>
       </c>
       <c r="H151" t="n">
-        <v>16074.937801</v>
+        <v>16074.326467</v>
       </c>
       <c r="I151" t="n">
-        <v>17867.737368</v>
+        <v>17868.229079</v>
       </c>
       <c r="J151" t="n">
         <v>18821.241109</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>18480.359917</v>
+        <v>18473.589813</v>
       </c>
       <c r="F152" t="n">
-        <v>20188.960611</v>
+        <v>20225.515013</v>
       </c>
       <c r="G152" t="n">
-        <v>22217.19882</v>
+        <v>22250.039156</v>
       </c>
       <c r="H152" t="n">
-        <v>24193.256075</v>
+        <v>24213.247132</v>
       </c>
       <c r="I152" t="n">
-        <v>26633.800397</v>
+        <v>26641.942377</v>
       </c>
       <c r="J152" t="n">
         <v>27670.126643</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6930.085238</v>
+        <v>6707.498806</v>
       </c>
       <c r="F153" t="n">
-        <v>8758.571548</v>
+        <v>8620.254274000001</v>
       </c>
       <c r="G153" t="n">
-        <v>10474.090741</v>
+        <v>10382.094302</v>
       </c>
       <c r="H153" t="n">
-        <v>11959.429862</v>
+        <v>11903.221585</v>
       </c>
       <c r="I153" t="n">
-        <v>13549.551132</v>
+        <v>13522.2767</v>
       </c>
       <c r="J153" t="n">
         <v>14476.115903</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1637.533985</v>
+        <v>1638.667209</v>
       </c>
       <c r="F154" t="n">
-        <v>1726.231266</v>
+        <v>1731.002245</v>
       </c>
       <c r="G154" t="n">
-        <v>1828.33394</v>
+        <v>1832.914455</v>
       </c>
       <c r="H154" t="n">
-        <v>1922.576305</v>
+        <v>1925.747747</v>
       </c>
       <c r="I154" t="n">
-        <v>2058.59897</v>
+        <v>2060.105446</v>
       </c>
       <c r="J154" t="n">
         <v>2097.849179</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6407.512892</v>
+        <v>6044.346986</v>
       </c>
       <c r="F155" t="n">
-        <v>10590.553662</v>
+        <v>10269.965605</v>
       </c>
       <c r="G155" t="n">
-        <v>14814.483537</v>
+        <v>14555.388433</v>
       </c>
       <c r="H155" t="n">
-        <v>19240.445009</v>
+        <v>19054.499572</v>
       </c>
       <c r="I155" t="n">
-        <v>23264.799464</v>
+        <v>23166.788412</v>
       </c>
       <c r="J155" t="n">
         <v>26622.676755</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>23178.416475</v>
+        <v>23508.947749</v>
       </c>
       <c r="F156" t="n">
-        <v>32818.247999</v>
+        <v>33120.539422</v>
       </c>
       <c r="G156" t="n">
-        <v>40056.807156</v>
+        <v>40295.827691</v>
       </c>
       <c r="H156" t="n">
-        <v>45665.470417</v>
+        <v>45829.415941</v>
       </c>
       <c r="I156" t="n">
-        <v>48920.525654</v>
+        <v>49003.173977</v>
       </c>
       <c r="J156" t="n">
         <v>49687.875941</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>154.137413</v>
+        <v>224.775926</v>
       </c>
       <c r="F157" t="n">
-        <v>167.622213</v>
+        <v>240.443293</v>
       </c>
       <c r="G157" t="n">
-        <v>169.308487</v>
+        <v>234.468214</v>
       </c>
       <c r="H157" t="n">
-        <v>161.349379</v>
+        <v>208.665112</v>
       </c>
       <c r="I157" t="n">
-        <v>146.776541</v>
+        <v>170.477655</v>
       </c>
       <c r="J157" t="n">
         <v>130.095399</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2020.883546</v>
+        <v>2052.930743</v>
       </c>
       <c r="F158" t="n">
-        <v>2891.554623</v>
+        <v>2898.383101</v>
       </c>
       <c r="G158" t="n">
-        <v>3615.076632</v>
+        <v>3606.166803</v>
       </c>
       <c r="H158" t="n">
-        <v>4190.480421</v>
+        <v>4179.282907</v>
       </c>
       <c r="I158" t="n">
-        <v>4520.765268</v>
+        <v>4514.219365</v>
       </c>
       <c r="J158" t="n">
         <v>4593.00104</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>48.352698</v>
+        <v>63.456862</v>
       </c>
       <c r="F159" t="n">
-        <v>55.759368</v>
+        <v>67.28257499999999</v>
       </c>
       <c r="G159" t="n">
-        <v>62.401855</v>
+        <v>70.529332</v>
       </c>
       <c r="H159" t="n">
-        <v>68.08280499999999</v>
+        <v>73.209591</v>
       </c>
       <c r="I159" t="n">
-        <v>71.1251</v>
+        <v>73.554154</v>
       </c>
       <c r="J159" t="n">
         <v>71.399505</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5222.084668</v>
+        <v>5136.929426</v>
       </c>
       <c r="F160" t="n">
-        <v>8057.598953</v>
+        <v>7984.722823</v>
       </c>
       <c r="G160" t="n">
-        <v>10495.417284</v>
+        <v>10451.114478</v>
       </c>
       <c r="H160" t="n">
-        <v>12667.809437</v>
+        <v>12648.564346</v>
       </c>
       <c r="I160" t="n">
-        <v>14329.607332</v>
+        <v>14325.385795</v>
       </c>
       <c r="J160" t="n">
         <v>15546.941681</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>422.474821</v>
+        <v>594.219198</v>
       </c>
       <c r="F162" t="n">
-        <v>313.624517</v>
+        <v>387.527648</v>
       </c>
       <c r="G162" t="n">
-        <v>320.966488</v>
+        <v>354.619648</v>
       </c>
       <c r="H162" t="n">
-        <v>372.836661</v>
+        <v>388.918579</v>
       </c>
       <c r="I162" t="n">
-        <v>423.697069</v>
+        <v>430.137368</v>
       </c>
       <c r="J162" t="n">
         <v>458.200423</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>717.176487</v>
+        <v>697.3302</v>
       </c>
       <c r="F163" t="n">
-        <v>824.394435</v>
+        <v>813.014003</v>
       </c>
       <c r="G163" t="n">
-        <v>836.791647</v>
+        <v>830.80173</v>
       </c>
       <c r="H163" t="n">
-        <v>867.86977</v>
+        <v>864.760713</v>
       </c>
       <c r="I163" t="n">
-        <v>890.010677</v>
+        <v>888.690378</v>
       </c>
       <c r="J163" t="n">
         <v>897.561968</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>16978.966044</v>
+        <v>16233.596128</v>
       </c>
       <c r="F164" t="n">
-        <v>19472.574299</v>
+        <v>19016.41601</v>
       </c>
       <c r="G164" t="n">
-        <v>19827.575923</v>
+        <v>19544.822674</v>
       </c>
       <c r="H164" t="n">
-        <v>20494.539478</v>
+        <v>20326.779657</v>
       </c>
       <c r="I164" t="n">
-        <v>20868.856022</v>
+        <v>20792.837905</v>
       </c>
       <c r="J164" t="n">
         <v>20933.395522</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6532.907166</v>
+        <v>6378.104691</v>
       </c>
       <c r="F165" t="n">
-        <v>8305.181988</v>
+        <v>8196.138472000001</v>
       </c>
       <c r="G165" t="n">
-        <v>10084.970087</v>
+        <v>9990.732536</v>
       </c>
       <c r="H165" t="n">
-        <v>12178.411738</v>
+        <v>12105.207984</v>
       </c>
       <c r="I165" t="n">
-        <v>13984.816406</v>
+        <v>13944.609334</v>
       </c>
       <c r="J165" t="n">
         <v>15387.148099</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>72357.209875</v>
+        <v>69298.404996</v>
       </c>
       <c r="F166" t="n">
-        <v>88511.126755</v>
+        <v>86465.82924399999</v>
       </c>
       <c r="G166" t="n">
-        <v>96747.895531</v>
+        <v>95345.545287</v>
       </c>
       <c r="H166" t="n">
-        <v>105390.395078</v>
+        <v>104487.977803</v>
       </c>
       <c r="I166" t="n">
-        <v>110760.505978</v>
+        <v>110327.934793</v>
       </c>
       <c r="J166" t="n">
         <v>112560.1945</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>21968.318452</v>
+        <v>25328.558644</v>
       </c>
       <c r="F167" t="n">
-        <v>24366.212438</v>
+        <v>26400.015353</v>
       </c>
       <c r="G167" t="n">
-        <v>26818.197963</v>
+        <v>28130.690534</v>
       </c>
       <c r="H167" t="n">
-        <v>29809.655492</v>
+        <v>30650.714695</v>
       </c>
       <c r="I167" t="n">
-        <v>32010.298626</v>
+        <v>32428.584244</v>
       </c>
       <c r="J167" t="n">
         <v>33199.667116</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>315.730305</v>
+        <v>381.568029</v>
       </c>
       <c r="F168" t="n">
-        <v>323.501338</v>
+        <v>368.677005</v>
       </c>
       <c r="G168" t="n">
-        <v>333.609391</v>
+        <v>365.775917</v>
       </c>
       <c r="H168" t="n">
-        <v>353.461714</v>
+        <v>375.057252</v>
       </c>
       <c r="I168" t="n">
-        <v>367.927568</v>
+        <v>378.764202</v>
       </c>
       <c r="J168" t="n">
         <v>374.038466</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>104007.102918</v>
+        <v>100449.261486</v>
       </c>
       <c r="F169" t="n">
-        <v>140273.824559</v>
+        <v>137551.283263</v>
       </c>
       <c r="G169" t="n">
-        <v>171023.681883</v>
+        <v>168881.681752</v>
       </c>
       <c r="H169" t="n">
-        <v>204607.068789</v>
+        <v>203079.34554</v>
       </c>
       <c r="I169" t="n">
-        <v>232091.375897</v>
+        <v>231305.366981</v>
       </c>
       <c r="J169" t="n">
         <v>252621.091863</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>7111.440089</v>
+        <v>6842.305163</v>
       </c>
       <c r="F170" t="n">
-        <v>8605.379800000001</v>
+        <v>8439.201365000001</v>
       </c>
       <c r="G170" t="n">
-        <v>9637.966748000001</v>
+        <v>9528.231143999999</v>
       </c>
       <c r="H170" t="n">
-        <v>11153.405099</v>
+        <v>11080.80151</v>
       </c>
       <c r="I170" t="n">
-        <v>12670.416748</v>
+        <v>12633.194958</v>
       </c>
       <c r="J170" t="n">
         <v>14039.504304</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>18471.422503</v>
+        <v>18470.32721</v>
       </c>
       <c r="F171" t="n">
-        <v>21772.983834</v>
+        <v>21762.670764</v>
       </c>
       <c r="G171" t="n">
-        <v>23477.595689</v>
+        <v>23467.30639</v>
       </c>
       <c r="H171" t="n">
-        <v>25340.759459</v>
+        <v>25333.049986</v>
       </c>
       <c r="I171" t="n">
-        <v>26508.663064</v>
+        <v>26504.416084</v>
       </c>
       <c r="J171" t="n">
         <v>26848.793442</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3605.711183</v>
+        <v>4917.388698</v>
       </c>
       <c r="F172" t="n">
-        <v>2984.079071</v>
+        <v>3803.992143</v>
       </c>
       <c r="G172" t="n">
-        <v>2720.544755</v>
+        <v>3237.860319</v>
       </c>
       <c r="H172" t="n">
-        <v>2678.357493</v>
+        <v>2990.511585</v>
       </c>
       <c r="I172" t="n">
-        <v>2646.504602</v>
+        <v>2791.861087</v>
       </c>
       <c r="J172" t="n">
         <v>2574.525251</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>685.17407</v>
+        <v>654.801962</v>
       </c>
       <c r="F173" t="n">
-        <v>873.574444</v>
+        <v>852.712055</v>
       </c>
       <c r="G173" t="n">
-        <v>1015.238597</v>
+        <v>1000.180675</v>
       </c>
       <c r="H173" t="n">
-        <v>1206.534687</v>
+        <v>1196.004587</v>
       </c>
       <c r="I173" t="n">
-        <v>1394.909268</v>
+        <v>1389.366356</v>
       </c>
       <c r="J173" t="n">
         <v>1565.358915</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>50249.997755</v>
+        <v>53681.105945</v>
       </c>
       <c r="F174" t="n">
-        <v>57372.450933</v>
+        <v>59387.686998</v>
       </c>
       <c r="G174" t="n">
-        <v>62046.813919</v>
+        <v>63292.894627</v>
       </c>
       <c r="H174" t="n">
-        <v>67122.983897</v>
+        <v>67890.479466</v>
       </c>
       <c r="I174" t="n">
-        <v>69849.282236</v>
+        <v>70220.483289</v>
       </c>
       <c r="J174" t="n">
         <v>69433.427893</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1823.745529</v>
+        <v>1750.286288</v>
       </c>
       <c r="F175" t="n">
-        <v>2149.947041</v>
+        <v>2106.453083</v>
       </c>
       <c r="G175" t="n">
-        <v>2338.13727</v>
+        <v>2311.560299</v>
       </c>
       <c r="H175" t="n">
-        <v>2628.1343</v>
+        <v>2612.369403</v>
       </c>
       <c r="I175" t="n">
-        <v>2889.206685</v>
+        <v>2882.213995</v>
       </c>
       <c r="J175" t="n">
         <v>3111.796677</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>64.88166099999999</v>
+        <v>62.665633</v>
       </c>
       <c r="F176" t="n">
-        <v>85.25395399999999</v>
+        <v>83.545962</v>
       </c>
       <c r="G176" t="n">
-        <v>98.666175</v>
+        <v>97.38682900000001</v>
       </c>
       <c r="H176" t="n">
-        <v>112.011855</v>
+        <v>111.144795</v>
       </c>
       <c r="I176" t="n">
-        <v>120.783937</v>
+        <v>120.358596</v>
       </c>
       <c r="J176" t="n">
         <v>125.466866</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>83881.025048</v>
+        <v>83464.07311899999</v>
       </c>
       <c r="F177" t="n">
-        <v>90524.136732</v>
+        <v>91130.753856</v>
       </c>
       <c r="G177" t="n">
-        <v>90528.11138</v>
+        <v>91482.318581</v>
       </c>
       <c r="H177" t="n">
-        <v>93905.830187</v>
+        <v>94733.045383</v>
       </c>
       <c r="I177" t="n">
-        <v>97300.487056</v>
+        <v>97740.93779700001</v>
       </c>
       <c r="J177" t="n">
         <v>99497.482041</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>170.334882</v>
+        <v>163.27151</v>
       </c>
       <c r="F178" t="n">
-        <v>226.80219</v>
+        <v>221.675923</v>
       </c>
       <c r="G178" t="n">
-        <v>274.074188</v>
+        <v>270.183419</v>
       </c>
       <c r="H178" t="n">
-        <v>331.309816</v>
+        <v>328.526345</v>
       </c>
       <c r="I178" t="n">
-        <v>385.973569</v>
+        <v>384.492452</v>
       </c>
       <c r="J178" t="n">
         <v>433.915574</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>121.287759</v>
+        <v>117.637645</v>
       </c>
       <c r="F179" t="n">
-        <v>149.497054</v>
+        <v>146.952234</v>
       </c>
       <c r="G179" t="n">
-        <v>164.355481</v>
+        <v>162.600752</v>
       </c>
       <c r="H179" t="n">
-        <v>180.591489</v>
+        <v>179.461719</v>
       </c>
       <c r="I179" t="n">
-        <v>190.731684</v>
+        <v>190.197272</v>
       </c>
       <c r="J179" t="n">
         <v>194.087104</v>
@@ -14130,58 +14130,58 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>-5e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="F181" t="n">
-        <v>-5e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="G181" t="n">
-        <v>-1e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="H181" t="n">
-        <v>3e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="I181" t="n">
-        <v>-0</v>
+        <v>-7e-06</v>
       </c>
       <c r="J181" t="n">
-        <v>7e-06</v>
+        <v>5e-06</v>
       </c>
       <c r="K181" t="n">
         <v>-6e-06</v>
       </c>
       <c r="L181" t="n">
-        <v>-2e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="M181" t="n">
-        <v>8e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="N181" t="n">
-        <v>-1e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="O181" t="n">
-        <v>-0</v>
+        <v>2e-06</v>
       </c>
       <c r="P181" t="n">
-        <v>-2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="Q181" t="n">
         <v>1e-06</v>
       </c>
       <c r="R181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="S181" t="n">
         <v>-2e-06</v>
-      </c>
-      <c r="S181" t="n">
-        <v>-1e-06</v>
       </c>
       <c r="T181" t="n">
         <v>-2e-06</v>
       </c>
       <c r="U181" t="n">
-        <v>-1e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>-2e-06</v>
+        <v>-5e-06</v>
       </c>
     </row>
   </sheetData>
